--- a/public/exports/29189447.xlsx
+++ b/public/exports/29189447.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042618</t>
+          <t xml:space="preserve">200042632</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -12514,12 +12514,12 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865119</t>
+          <t xml:space="preserve">311865121</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t xml:space="preserve">CB Group ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -16264,7 +16264,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911466</t>
+          <t xml:space="preserve">311911471</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911823</t>
+          <t xml:space="preserve">311911826</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CB Group ApS</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -16714,12 +16714,12 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911823</t>
+          <t xml:space="preserve">311911826</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CB Group ApS</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">

--- a/public/exports/29189447.xlsx
+++ b/public/exports/29189447.xlsx
@@ -2366,30 +2366,30 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Centervænget 2</t>
+          <t xml:space="preserve">Tuse Byvej 26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399431</t>
+          <t xml:space="preserve">2393544</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J32">
-        <v>326</v>
+        <v>464</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219459</t>
+          <t xml:space="preserve">311219966</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2026-12-29</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Centervænget 4</t>
+          <t xml:space="preserve">Tuse Byvej 42</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399431</t>
+          <t xml:space="preserve">2393544</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2460,11 +2460,11 @@
         </is>
       </c>
       <c r="J33">
-        <v>400</v>
+        <v>464</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219459</t>
+          <t xml:space="preserve">311219966</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2026-12-29</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 26</t>
+          <t xml:space="preserve">Tuse Byvej 58</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J34">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 42</t>
+          <t xml:space="preserve">Tuse Byvej 74</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J35">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 58</t>
+          <t xml:space="preserve">Bispehøjen 4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2676,20 +2676,20 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393544</t>
+          <t xml:space="preserve">5336543</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J36">
-        <v>464</v>
+        <v>606</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219966</t>
+          <t xml:space="preserve">311220222</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-29</t>
+          <t xml:space="preserve">2027-01-02</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 74</t>
+          <t xml:space="preserve">Gasværksvej 9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2751,20 +2751,20 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393544</t>
+          <t xml:space="preserve">5334816</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J37">
-        <v>464</v>
+        <v>1192</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219966</t>
+          <t xml:space="preserve">311220229</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-29</t>
+          <t xml:space="preserve">2027-01-02</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bispehøjen 4</t>
+          <t xml:space="preserve">Parallelvej 52</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2826,20 +2826,20 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5336543</t>
+          <t xml:space="preserve">5335410</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J38">
-        <v>606</v>
+        <v>288</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220222</t>
+          <t xml:space="preserve">311220230</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasværksvej 9</t>
+          <t xml:space="preserve">Konsul Beÿers Allé 1A</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334816</t>
+          <t xml:space="preserve">8366959</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2910,11 +2910,11 @@
         </is>
       </c>
       <c r="J39">
-        <v>1192</v>
+        <v>509</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220229</t>
+          <t xml:space="preserve">311220673</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-02</t>
+          <t xml:space="preserve">2027-01-04</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 52</t>
+          <t xml:space="preserve">Tuse Byvej 24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2976,20 +2976,20 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335410</t>
+          <t xml:space="preserve">265751, 265752</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J40">
-        <v>288</v>
+        <v>939</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220230</t>
+          <t xml:space="preserve">311222478</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-02</t>
+          <t xml:space="preserve">2027-01-13</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Konsul Beÿers Allé 1A</t>
+          <t xml:space="preserve">Sønderstrupvej 26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">8366959</t>
+          <t xml:space="preserve">100078242</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3060,21 +3060,21 @@
         </is>
       </c>
       <c r="J41">
-        <v>509</v>
+        <v>6249</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220673</t>
+          <t xml:space="preserve">311225362</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+          <t xml:space="preserve">John Klysner Consult ApS</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-04</t>
+          <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 24</t>
+          <t xml:space="preserve">Kasernevej 6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">265751, 265752</t>
+          <t xml:space="preserve">8033723</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3135,11 +3135,11 @@
         </is>
       </c>
       <c r="J42">
-        <v>939</v>
+        <v>2314</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311222478</t>
+          <t xml:space="preserve">311229616</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-13</t>
+          <t xml:space="preserve">2027-02-21</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3191,17 +3191,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderstrupvej 26</t>
+          <t xml:space="preserve">Rørvangsvej 4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">100078242</t>
+          <t xml:space="preserve">5340673</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3210,21 +3210,21 @@
         </is>
       </c>
       <c r="J43">
-        <v>6249</v>
+        <v>1017</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225362</t>
+          <t xml:space="preserve">311233036</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Klysner Consult ApS</t>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-30</t>
+          <t xml:space="preserve">2027-03-09</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kasernevej 6</t>
+          <t xml:space="preserve">Karensmindevej 7</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">8033723</t>
+          <t xml:space="preserve">5335611</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3285,11 +3285,11 @@
         </is>
       </c>
       <c r="J44">
-        <v>2314</v>
+        <v>1170</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229616</t>
+          <t xml:space="preserve">311233787</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-21</t>
+          <t xml:space="preserve">2027-03-13</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rørvangsvej 4</t>
+          <t xml:space="preserve">Munkevænget 38</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340673</t>
+          <t xml:space="preserve">5336544</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3360,11 +3360,11 @@
         </is>
       </c>
       <c r="J45">
-        <v>1017</v>
+        <v>730</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233036</t>
+          <t xml:space="preserve">311233788</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-09</t>
+          <t xml:space="preserve">2027-03-13</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karensmindevej 7</t>
+          <t xml:space="preserve">Carl Reffsvej 2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335611</t>
+          <t xml:space="preserve">270089</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3435,11 +3435,11 @@
         </is>
       </c>
       <c r="J46">
-        <v>1170</v>
+        <v>2052</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233787</t>
+          <t xml:space="preserve">311234340</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-13</t>
+          <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Munkevænget 38</t>
+          <t xml:space="preserve">Carl Reffsvej 32</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3501,20 +3501,20 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5336544</t>
+          <t xml:space="preserve">5335507</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J47">
-        <v>730</v>
+        <v>306</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233788</t>
+          <t xml:space="preserve">311234425</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-13</t>
+          <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Reffsvej 2</t>
+          <t xml:space="preserve">Carl Reffsvej 42</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3576,20 +3576,20 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">270089</t>
+          <t xml:space="preserve">5335507</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J48">
-        <v>2052</v>
+        <v>1244</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234340</t>
+          <t xml:space="preserve">311234435</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Reffsvej 32</t>
+          <t xml:space="preserve">Carl Reffsvej 78</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J49">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Reffsvej 42</t>
+          <t xml:space="preserve">Carl Reffsvej 8</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3731,15 +3731,15 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J50">
-        <v>1244</v>
+        <v>412</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234435</t>
+          <t xml:space="preserve">311234425</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Reffsvej 78</t>
+          <t xml:space="preserve">Carl Reffsvej 88</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3806,15 +3806,15 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J51">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234425</t>
+          <t xml:space="preserve">311234423</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Reffsvej 8</t>
+          <t xml:space="preserve">Stenhusvej 23A</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3876,20 +3876,20 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335507</t>
+          <t xml:space="preserve">7573379</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J52">
-        <v>412</v>
+        <v>512</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234425</t>
+          <t xml:space="preserve">311236497</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-15</t>
+          <t xml:space="preserve">2027-03-24</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Reffsvej 88</t>
+          <t xml:space="preserve">Stenhusvej 25A</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3951,20 +3951,20 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335507</t>
+          <t xml:space="preserve">7573379</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J53">
-        <v>303</v>
+        <v>512</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234423</t>
+          <t xml:space="preserve">311236497</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-15</t>
+          <t xml:space="preserve">2027-03-24</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemvang 9</t>
+          <t xml:space="preserve">Stenhusvej 27A</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340827</t>
+          <t xml:space="preserve">7573379</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J54">
-        <v>1983</v>
+        <v>512</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234426</t>
+          <t xml:space="preserve">311236497</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-15</t>
+          <t xml:space="preserve">2027-03-24</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenhusvej 23A</t>
+          <t xml:space="preserve">Stenhusvej 29A</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J55">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenhusvej 25A</t>
+          <t xml:space="preserve">Stenhusvej 31A</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J56">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenhusvej 27A</t>
+          <t xml:space="preserve">Stenhusvej 21</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4251,20 +4251,20 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">7573379</t>
+          <t xml:space="preserve">271115, 271116</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J57">
-        <v>512</v>
+        <v>6192</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236497</t>
+          <t xml:space="preserve">311237694</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-24</t>
+          <t xml:space="preserve">2027-03-30</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenhusvej 29A</t>
+          <t xml:space="preserve">Gl Tuse Næs Vej 15A</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4326,20 +4326,20 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">7573379</t>
+          <t xml:space="preserve">272010, 272011</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J58">
-        <v>512</v>
+        <v>1658</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236497</t>
+          <t xml:space="preserve">311239402</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-24</t>
+          <t xml:space="preserve">2027-04-06</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenhusvej 31A</t>
+          <t xml:space="preserve">Gl Tuse Næs Vej 15B</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4401,20 +4401,20 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">7573379</t>
+          <t xml:space="preserve">272010</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J59">
-        <v>512</v>
+        <v>1846</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236497</t>
+          <t xml:space="preserve">311239403</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-24</t>
+          <t xml:space="preserve">2027-04-06</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenhusvej 21</t>
+          <t xml:space="preserve">Tidemandsvej 1A</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4476,30 +4476,30 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">271115, 271116</t>
+          <t xml:space="preserve">5335169</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J60">
-        <v>6192</v>
+        <v>641</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311237694</t>
+          <t xml:space="preserve">311239463</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-30</t>
+          <t xml:space="preserve">2027-04-06</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Tuse Næs Vej 15A</t>
+          <t xml:space="preserve">Kattegatsvej 11</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">272010, 272011</t>
+          <t xml:space="preserve">8077237</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4560,11 +4560,11 @@
         </is>
       </c>
       <c r="J61">
-        <v>1658</v>
+        <v>470</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311239402</t>
+          <t xml:space="preserve">311242885</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-06</t>
+          <t xml:space="preserve">2027-04-25</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Tuse Næs Vej 15B</t>
+          <t xml:space="preserve">Jernbanevej 6</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4626,20 +4626,20 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">272010</t>
+          <t xml:space="preserve">5334983</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J62">
-        <v>1846</v>
+        <v>8718</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311239403</t>
+          <t xml:space="preserve">311243219</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-06</t>
+          <t xml:space="preserve">2027-04-26</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tidemandsvej 1A</t>
+          <t xml:space="preserve">Rolighedsstræde 2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4701,30 +4701,30 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335169</t>
+          <t xml:space="preserve">5334475</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J63">
-        <v>641</v>
+        <v>256</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311239463</t>
+          <t xml:space="preserve">311243209</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-06</t>
+          <t xml:space="preserve">2027-04-26</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kattegatsvej 11</t>
+          <t xml:space="preserve">Rolighedsstræde 5</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">8077237</t>
+          <t xml:space="preserve">5334947</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4785,11 +4785,11 @@
         </is>
       </c>
       <c r="J64">
-        <v>470</v>
+        <v>410</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242885</t>
+          <t xml:space="preserve">311243212</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-25</t>
+          <t xml:space="preserve">2027-04-26</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanevej 6</t>
+          <t xml:space="preserve">Roskildevej 12</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334983</t>
+          <t xml:space="preserve">7805439</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4860,16 +4860,16 @@
         </is>
       </c>
       <c r="J65">
-        <v>8718</v>
+        <v>540</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243219</t>
+          <t xml:space="preserve">311243217</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4916,17 +4916,17 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolighedsstræde 2</t>
+          <t xml:space="preserve">Ellebjergvej 31B</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334475</t>
+          <t xml:space="preserve">100044734</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4935,21 +4935,21 @@
         </is>
       </c>
       <c r="J66">
-        <v>256</v>
+        <v>615</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243209</t>
+          <t xml:space="preserve">311248907</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-26</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4991,17 +4991,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolighedsstræde 5</t>
+          <t xml:space="preserve">Hjortholmvej 9A</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334947</t>
+          <t xml:space="preserve">2409849</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5010,21 +5010,21 @@
         </is>
       </c>
       <c r="J67">
-        <v>410</v>
+        <v>1876</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243212</t>
+          <t xml:space="preserve">311248975</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-26</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskildevej 12</t>
+          <t xml:space="preserve">Kikhøjparken 1</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">7805439</t>
+          <t xml:space="preserve">5339293</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="J68">
-        <v>540</v>
+        <v>1227</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243217</t>
+          <t xml:space="preserve">311249402</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-26</t>
+          <t xml:space="preserve">2027-05-23</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ellebjergvej 31B</t>
+          <t xml:space="preserve">Blomstervænget 2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4420</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">100044734</t>
+          <t xml:space="preserve">7637708</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5160,11 +5160,11 @@
         </is>
       </c>
       <c r="J69">
-        <v>615</v>
+        <v>872</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248907</t>
+          <t xml:space="preserve">311250302</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-05-29</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5216,17 +5216,17 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjortholmvej 9A</t>
+          <t xml:space="preserve">Byparken 2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4520</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2409849</t>
+          <t xml:space="preserve">2392048</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5235,21 +5235,21 @@
         </is>
       </c>
       <c r="J70">
-        <v>1876</v>
+        <v>1053</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248975</t>
+          <t xml:space="preserve">311251071</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-05-31</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5291,17 +5291,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kikhøjparken 1</t>
+          <t xml:space="preserve">Gl. Skovvej 150C</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4420</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339293</t>
+          <t xml:space="preserve">2401337</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5310,11 +5310,11 @@
         </is>
       </c>
       <c r="J71">
-        <v>1227</v>
+        <v>1128</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311249402</t>
+          <t xml:space="preserve">311251192</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-23</t>
+          <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blomstervænget 2</t>
+          <t xml:space="preserve">Gl. Skovvej 150C</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5376,20 +5376,20 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">7637708</t>
+          <t xml:space="preserve">2401337</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J72">
-        <v>872</v>
+        <v>1731</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311250302</t>
+          <t xml:space="preserve">311251192</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-29</t>
+          <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5441,30 +5441,30 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byparken 2</t>
+          <t xml:space="preserve">Gl. Skovvej 150C</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">4520</t>
+          <t xml:space="preserve">4420</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2392048</t>
+          <t xml:space="preserve">2401337</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J73">
-        <v>1053</v>
+        <v>2223</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251071</t>
+          <t xml:space="preserve">311251192</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-31</t>
+          <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5531,11 +5531,11 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J74">
-        <v>1128</v>
+        <v>795</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -5591,17 +5591,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Skovvej 150C</t>
+          <t xml:space="preserve">Damvej 14A</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4420</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2401337</t>
+          <t xml:space="preserve">2384645</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5610,11 +5610,11 @@
         </is>
       </c>
       <c r="J75">
-        <v>1731</v>
+        <v>799</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251192</t>
+          <t xml:space="preserve">311251899</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-01</t>
+          <t xml:space="preserve">2027-06-06</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5666,30 +5666,30 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Skovvej 150C</t>
+          <t xml:space="preserve">Damvej 14B</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4420</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2401337</t>
+          <t xml:space="preserve">2384645</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J76">
-        <v>2223</v>
+        <v>439</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251192</t>
+          <t xml:space="preserve">311251898</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-01</t>
+          <t xml:space="preserve">2027-06-06</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Skovvej 150C</t>
+          <t xml:space="preserve">Holløsevej 10C</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5751,20 +5751,20 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2401337</t>
+          <t xml:space="preserve">2401302</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J77">
-        <v>795</v>
+        <v>564</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251192</t>
+          <t xml:space="preserve">311258791</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-01</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5816,30 +5816,30 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damvej 14A</t>
+          <t xml:space="preserve">Hovedgaden 40</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2384645</t>
+          <t xml:space="preserve">9415784</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J78">
-        <v>799</v>
+        <v>1014</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251899</t>
+          <t xml:space="preserve">311258739</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5891,17 +5891,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damvej 14B</t>
+          <t xml:space="preserve">Hovedgaden 59</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4520</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2384645</t>
+          <t xml:space="preserve">2391781</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5910,11 +5910,11 @@
         </is>
       </c>
       <c r="J79">
-        <v>439</v>
+        <v>999</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251898</t>
+          <t xml:space="preserve">311258737</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5966,17 +5966,17 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holløsevej 10C</t>
+          <t xml:space="preserve">Jernbanevej 18E</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">4420</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2401302</t>
+          <t xml:space="preserve">2408920</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5985,11 +5985,11 @@
         </is>
       </c>
       <c r="J80">
-        <v>564</v>
+        <v>754</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258791</t>
+          <t xml:space="preserve">311258825</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 40</t>
+          <t xml:space="preserve">Nytorv 14</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6051,20 +6051,20 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">9415784</t>
+          <t xml:space="preserve">2408839</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J81">
-        <v>1014</v>
+        <v>840</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258739</t>
+          <t xml:space="preserve">311264148</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-08-02</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 59</t>
+          <t xml:space="preserve">Svinningehallen 1</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391781</t>
+          <t xml:space="preserve">719759, 2391621</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -6135,11 +6135,11 @@
         </is>
       </c>
       <c r="J82">
-        <v>999</v>
+        <v>3125</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258737</t>
+          <t xml:space="preserve">311350102</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-05</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanevej 18E</t>
+          <t xml:space="preserve">Øvej 5A</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408920</t>
+          <t xml:space="preserve">2402709</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -6210,11 +6210,11 @@
         </is>
       </c>
       <c r="J83">
-        <v>754</v>
+        <v>1724</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258825</t>
+          <t xml:space="preserve">311272027</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-11</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nytorv 14</t>
+          <t xml:space="preserve">Øvej 5B</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6276,20 +6276,20 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408839</t>
+          <t xml:space="preserve">2402709</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J84">
-        <v>840</v>
+        <v>346</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264148</t>
+          <t xml:space="preserve">311272304</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-02</t>
+          <t xml:space="preserve">2027-09-12</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6341,17 +6341,17 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svinningehallen 1</t>
+          <t xml:space="preserve">Markedspladsen 6A</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">4520</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">719759, 2391621</t>
+          <t xml:space="preserve">5334610</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -6360,11 +6360,11 @@
         </is>
       </c>
       <c r="J85">
-        <v>3125</v>
+        <v>472</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311350102</t>
+          <t xml:space="preserve">311274663</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-05</t>
+          <t xml:space="preserve">2027-09-22</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øvej 5A</t>
+          <t xml:space="preserve">Sportsvej 2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402709</t>
+          <t xml:space="preserve">719772, 2409825</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -6435,11 +6435,11 @@
         </is>
       </c>
       <c r="J86">
-        <v>1724</v>
+        <v>2306</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272027</t>
+          <t xml:space="preserve">311276692</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-11</t>
+          <t xml:space="preserve">2027-10-04</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øvej 5B</t>
+          <t xml:space="preserve">Østergade 64</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6501,20 +6501,20 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402709</t>
+          <t xml:space="preserve">2408814</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J87">
-        <v>346</v>
+        <v>459</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272304</t>
+          <t xml:space="preserve">311276699</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-12</t>
+          <t xml:space="preserve">2027-10-04</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6566,30 +6566,30 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Markedspladsen 6A</t>
+          <t xml:space="preserve">Øvej 3</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334610</t>
+          <t xml:space="preserve">9415784</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J88">
-        <v>472</v>
+        <v>1030</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311274663</t>
+          <t xml:space="preserve">311276724</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-22</t>
+          <t xml:space="preserve">2027-10-04</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 2</t>
+          <t xml:space="preserve">Øvej 3</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6651,20 +6651,20 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">719772, 2409825</t>
+          <t xml:space="preserve">9415784</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J89">
-        <v>2306</v>
+        <v>1350</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276692</t>
+          <t xml:space="preserve">311276724</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 64</t>
+          <t xml:space="preserve">Øvej 3</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6726,20 +6726,20 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408814</t>
+          <t xml:space="preserve">9415784</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J90">
-        <v>459</v>
+        <v>820</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276699</t>
+          <t xml:space="preserve">311276724</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6791,30 +6791,30 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øvej 3</t>
+          <t xml:space="preserve">Ledegårdsvej 15</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4520</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">9415784</t>
+          <t xml:space="preserve">2391684</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J91">
-        <v>1030</v>
+        <v>278</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276724</t>
+          <t xml:space="preserve">311281139</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-04</t>
+          <t xml:space="preserve">2027-10-30</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6866,30 +6866,30 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øvej 3</t>
+          <t xml:space="preserve">Stormøllevej 9</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">9415784</t>
+          <t xml:space="preserve">5337399</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J92">
-        <v>1350</v>
+        <v>492</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276724</t>
+          <t xml:space="preserve">311282530</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-04</t>
+          <t xml:space="preserve">2027-11-07</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6941,30 +6941,30 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øvej 3</t>
+          <t xml:space="preserve">Ved Faurgården 7</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">9415784</t>
+          <t xml:space="preserve">5340353</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J93">
-        <v>820</v>
+        <v>745</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276724</t>
+          <t xml:space="preserve">311282521</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-04</t>
+          <t xml:space="preserve">2027-11-07</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7016,17 +7016,17 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ledegårdsvej 15</t>
+          <t xml:space="preserve">Industrivej 14B</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">4520</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391684</t>
+          <t xml:space="preserve">2409959</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -7035,11 +7035,11 @@
         </is>
       </c>
       <c r="J94">
-        <v>278</v>
+        <v>623</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311281139</t>
+          <t xml:space="preserve">311283082</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-30</t>
+          <t xml:space="preserve">2027-11-09</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7091,17 +7091,17 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stormøllevej 9</t>
+          <t xml:space="preserve">Kirkevej 1</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4532</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5337399</t>
+          <t xml:space="preserve">2384014</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -7110,11 +7110,11 @@
         </is>
       </c>
       <c r="J95">
-        <v>492</v>
+        <v>264</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282530</t>
+          <t xml:space="preserve">311283182</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-07</t>
+          <t xml:space="preserve">2027-11-09</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7166,30 +7166,30 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Faurgården 7</t>
+          <t xml:space="preserve">Kirkevej 1</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4532</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340353</t>
+          <t xml:space="preserve">2384014</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J96">
-        <v>745</v>
+        <v>400</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282521</t>
+          <t xml:space="preserve">311283182</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-07</t>
+          <t xml:space="preserve">2027-11-09</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7241,30 +7241,30 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 14B</t>
+          <t xml:space="preserve">Kirkevej 1</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4532</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2409959</t>
+          <t xml:space="preserve">2384014</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J97">
-        <v>623</v>
+        <v>553</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283082</t>
+          <t xml:space="preserve">311283182</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7316,17 +7316,17 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 1</t>
+          <t xml:space="preserve">Ringstedvej 43A</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">4532</t>
+          <t xml:space="preserve">4440</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2384014</t>
+          <t xml:space="preserve">2390836</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -7335,11 +7335,11 @@
         </is>
       </c>
       <c r="J98">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283182</t>
+          <t xml:space="preserve">311283188</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-09</t>
+          <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7391,30 +7391,30 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 1</t>
+          <t xml:space="preserve">Skarridsøgade 37</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">4532</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2384014</t>
+          <t xml:space="preserve">2388022</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J99">
-        <v>400</v>
+        <v>2632</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283182</t>
+          <t xml:space="preserve">311283186</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-09</t>
+          <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7466,30 +7466,30 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 1</t>
+          <t xml:space="preserve">Skarridsøgade 37A</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">4532</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2384014</t>
+          <t xml:space="preserve">2388022</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J100">
-        <v>553</v>
+        <v>528</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283182</t>
+          <t xml:space="preserve">311283186</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-09</t>
+          <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7541,17 +7541,17 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringstedvej 43A</t>
+          <t xml:space="preserve">Udbyvej 44</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4440</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2390836</t>
+          <t xml:space="preserve">2395636</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -7560,11 +7560,11 @@
         </is>
       </c>
       <c r="J101">
-        <v>262</v>
+        <v>396</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283188</t>
+          <t xml:space="preserve">311287525</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-10</t>
+          <t xml:space="preserve">2027-12-06</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7616,17 +7616,17 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skarridsøgade 37</t>
+          <t xml:space="preserve">Udbyvej 42</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2388022</t>
+          <t xml:space="preserve">2395380</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -7635,11 +7635,11 @@
         </is>
       </c>
       <c r="J102">
-        <v>2632</v>
+        <v>872</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283186</t>
+          <t xml:space="preserve">311287726</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-10</t>
+          <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7691,17 +7691,17 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skarridsøgade 37A</t>
+          <t xml:space="preserve">Udbyvej 42</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2388022</t>
+          <t xml:space="preserve">2395380</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -7710,11 +7710,11 @@
         </is>
       </c>
       <c r="J103">
-        <v>528</v>
+        <v>672</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283186</t>
+          <t xml:space="preserve">311287726</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-10</t>
+          <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udbyvej 44</t>
+          <t xml:space="preserve">Udbyvej 42</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7776,20 +7776,20 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395636</t>
+          <t xml:space="preserve">2395380</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J104">
-        <v>396</v>
+        <v>330</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287525</t>
+          <t xml:space="preserve">311287726</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-06</t>
+          <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7856,11 +7856,11 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J105">
-        <v>872</v>
+        <v>527</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udbyvej 42</t>
+          <t xml:space="preserve">Udby Kirkevej 21</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395380</t>
+          <t xml:space="preserve">2395597</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7935,11 +7935,11 @@
         </is>
       </c>
       <c r="J106">
-        <v>672</v>
+        <v>1691</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287726</t>
+          <t xml:space="preserve">311288089</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-07</t>
+          <t xml:space="preserve">2027-12-11</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udbyvej 42</t>
+          <t xml:space="preserve">Udby Kirkevej 23</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8001,20 +8001,20 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395380</t>
+          <t xml:space="preserve">2395597</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J107">
-        <v>330</v>
+        <v>2066</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287726</t>
+          <t xml:space="preserve">311289980</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-07</t>
+          <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udbyvej 42</t>
+          <t xml:space="preserve">Vandtårnsvej 6</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8076,20 +8076,20 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395380</t>
+          <t xml:space="preserve">5339301</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J108">
-        <v>527</v>
+        <v>503</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287726</t>
+          <t xml:space="preserve">311295412</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-07</t>
+          <t xml:space="preserve">2028-01-31</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8141,30 +8141,30 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udby Kirkevej 21</t>
+          <t xml:space="preserve">Lersøparken 142</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395597</t>
+          <t xml:space="preserve">7416498</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J109">
-        <v>1691</v>
+        <v>606</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288089</t>
+          <t xml:space="preserve">311307671</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-11</t>
+          <t xml:space="preserve">2028-04-11</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8216,17 +8216,17 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udby Kirkevej 23</t>
+          <t xml:space="preserve">Solvænget 1</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395597</t>
+          <t xml:space="preserve">2408810</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -8235,11 +8235,11 @@
         </is>
       </c>
       <c r="J110">
-        <v>2066</v>
+        <v>275</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289980</t>
+          <t xml:space="preserve">311307633</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-21</t>
+          <t xml:space="preserve">2028-04-11</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8291,30 +8291,30 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandtårnsvej 6</t>
+          <t xml:space="preserve">Solvænget 11</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339301</t>
+          <t xml:space="preserve">2408810</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J111">
-        <v>503</v>
+        <v>275</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295412</t>
+          <t xml:space="preserve">311307633</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-31</t>
+          <t xml:space="preserve">2028-04-11</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8366,30 +8366,30 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lersøparken 142</t>
+          <t xml:space="preserve">Solvænget 6</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">7416498</t>
+          <t xml:space="preserve">2408810</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J112">
-        <v>606</v>
+        <v>275</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307671</t>
+          <t xml:space="preserve">311307633</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8441,17 +8441,17 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solvænget 1</t>
+          <t xml:space="preserve">Højgårdsvej 24</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4350</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408810</t>
+          <t xml:space="preserve">2410722, 100800374</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -8460,11 +8460,11 @@
         </is>
       </c>
       <c r="J113">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307633</t>
+          <t xml:space="preserve">311307933</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-11</t>
+          <t xml:space="preserve">2028-04-12</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8516,30 +8516,30 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solvænget 11</t>
+          <t xml:space="preserve">Sofiesminde Alle 5</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408810</t>
+          <t xml:space="preserve">100011737</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J114">
-        <v>275</v>
+        <v>991</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307633</t>
+          <t xml:space="preserve">311308315</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-11</t>
+          <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8591,30 +8591,30 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solvænget 6</t>
+          <t xml:space="preserve">Tjørnegården 1</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408810</t>
+          <t xml:space="preserve">10055688</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J115">
-        <v>275</v>
+        <v>1354</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307633</t>
+          <t xml:space="preserve">311308295</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-11</t>
+          <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8666,30 +8666,30 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højgårdsvej 24</t>
+          <t xml:space="preserve">Havnevej 7</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">4350</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2410722, 100800374</t>
+          <t xml:space="preserve">5334808</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J116">
-        <v>262</v>
+        <v>1048</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307933</t>
+          <t xml:space="preserve">311342403</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-12</t>
+          <t xml:space="preserve">2028-10-19</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofiesminde Alle 5</t>
+          <t xml:space="preserve">Jernbanevej 29A</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">100011737</t>
+          <t xml:space="preserve">267924, 267925, 267926</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -8760,11 +8760,11 @@
         </is>
       </c>
       <c r="J117">
-        <v>991</v>
+        <v>600</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308315</t>
+          <t xml:space="preserve">311352731</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-13</t>
+          <t xml:space="preserve">2028-12-20</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8816,17 +8816,17 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnegården 1</t>
+          <t xml:space="preserve">Søbæksvej 30</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">10055688</t>
+          <t xml:space="preserve">270575</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -8835,11 +8835,11 @@
         </is>
       </c>
       <c r="J118">
-        <v>1354</v>
+        <v>2562</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308295</t>
+          <t xml:space="preserve">311354541</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-13</t>
+          <t xml:space="preserve">2029-01-14</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 7</t>
+          <t xml:space="preserve">Omfartsvejen 27</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8901,30 +8901,30 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334808</t>
+          <t xml:space="preserve">8282784</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J119">
-        <v>1048</v>
+        <v>353</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311342403</t>
+          <t xml:space="preserve">311403255</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-19</t>
+          <t xml:space="preserve">2029-10-10</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanevej 29A</t>
+          <t xml:space="preserve">Dampmøllevej 2</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">267924, 267925, 267926</t>
+          <t xml:space="preserve">7380402</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -8985,21 +8985,21 @@
         </is>
       </c>
       <c r="J120">
-        <v>600</v>
+        <v>1944</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352731</t>
+          <t xml:space="preserve">311448909</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-20</t>
+          <t xml:space="preserve">2030-07-09</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søbæksvej 30</t>
+          <t xml:space="preserve">Ladegårdsparken Vest 167</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">270575</t>
+          <t xml:space="preserve">5339287</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -9060,21 +9060,21 @@
         </is>
       </c>
       <c r="J121">
-        <v>2562</v>
+        <v>840</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311354541</t>
+          <t xml:space="preserve">311658138</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-14</t>
+          <t xml:space="preserve">2033-02-06</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9116,17 +9116,17 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omfartsvejen 27</t>
+          <t xml:space="preserve">Skolevej 37</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4440</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">8282784</t>
+          <t xml:space="preserve">2389399</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -9135,21 +9135,21 @@
         </is>
       </c>
       <c r="J122">
-        <v>353</v>
+        <v>1723</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311403255</t>
+          <t xml:space="preserve">311735788</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">ISOLINK ApS</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-10</t>
+          <t xml:space="preserve">2034-01-26</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,17 +9191,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dampmøllevej 2</t>
+          <t xml:space="preserve">Skolevej 4</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4532</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">7380402</t>
+          <t xml:space="preserve">2384021</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -9210,21 +9210,21 @@
         </is>
       </c>
       <c r="J123">
-        <v>1944</v>
+        <v>1872</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311448909</t>
+          <t xml:space="preserve">311834296</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">CB Group ApS</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-09</t>
+          <t xml:space="preserve">2035-05-26</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9266,40 +9266,40 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ladegårdsparken Vest 167</t>
+          <t xml:space="preserve">Skolevej 4</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4532</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339287</t>
+          <t xml:space="preserve">2384021</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J124">
-        <v>840</v>
+        <v>4238</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311658138</t>
+          <t xml:space="preserve">311834295</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">CB Group ApS</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-06</t>
+          <t xml:space="preserve">2035-05-26</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9341,17 +9341,17 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 37</t>
+          <t xml:space="preserve">Vandtårnsvej 3</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">4440</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2389399</t>
+          <t xml:space="preserve">10056287</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -9360,21 +9360,21 @@
         </is>
       </c>
       <c r="J125">
-        <v>1723</v>
+        <v>11883</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311735788</t>
+          <t xml:space="preserve">311834297</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISOLINK ApS</t>
+          <t xml:space="preserve">CB Group ApS</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-26</t>
+          <t xml:space="preserve">2035-05-26</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9416,17 +9416,17 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 4</t>
+          <t xml:space="preserve">Bispehøjen 2</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4532</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2384021</t>
+          <t xml:space="preserve">5338074</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -9435,11 +9435,11 @@
         </is>
       </c>
       <c r="J126">
-        <v>1872</v>
+        <v>1440</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311834296</t>
+          <t xml:space="preserve">311850583</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-26</t>
+          <t xml:space="preserve">2035-08-21</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9491,30 +9491,30 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 4</t>
+          <t xml:space="preserve">Bispehøjen 2</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">4532</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2384021</t>
+          <t xml:space="preserve">5338074</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J127">
-        <v>4238</v>
+        <v>301</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311834295</t>
+          <t xml:space="preserve">311850586</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-26</t>
+          <t xml:space="preserve">2035-08-21</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandtårnsvej 3</t>
+          <t xml:space="preserve">Bispehøjen 2</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9576,20 +9576,20 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">10056287</t>
+          <t xml:space="preserve">5338074</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J128">
-        <v>11883</v>
+        <v>1440</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311834297</t>
+          <t xml:space="preserve">311850583</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-26</t>
+          <t xml:space="preserve">2035-08-21</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9656,11 +9656,11 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J129">
-        <v>1440</v>
+        <v>1963</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -9731,15 +9731,15 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J130">
-        <v>301</v>
+        <v>477</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850584</t>
+          <t xml:space="preserve">311850583</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9806,11 +9806,11 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J131">
-        <v>1440</v>
+        <v>1685</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -9881,15 +9881,15 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J132">
-        <v>1963</v>
+        <v>2108</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850583</t>
+          <t xml:space="preserve">311850588</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9956,11 +9956,11 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J133">
-        <v>477</v>
+        <v>1440</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -10016,30 +10016,30 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bispehøjen 2</t>
+          <t xml:space="preserve">Holbækvej 108</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5338074</t>
+          <t xml:space="preserve">7226325</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J134">
-        <v>1685</v>
+        <v>1188</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850583</t>
+          <t xml:space="preserve">311851447</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-21</t>
+          <t xml:space="preserve">2035-08-26</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10091,30 +10091,30 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bispehøjen 2</t>
+          <t xml:space="preserve">Holbækvej 108</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5338074</t>
+          <t xml:space="preserve">7226325</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J135">
-        <v>2108</v>
+        <v>747</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850584</t>
+          <t xml:space="preserve">311851452</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-21</t>
+          <t xml:space="preserve">2035-08-26</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10166,30 +10166,30 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bispehøjen 2</t>
+          <t xml:space="preserve">Holbækvej 108</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5338074</t>
+          <t xml:space="preserve">7226325</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="J136">
-        <v>1440</v>
+        <v>431</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850583</t>
+          <t xml:space="preserve">311851447</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-21</t>
+          <t xml:space="preserve">2035-08-26</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10256,11 +10256,11 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J137">
-        <v>1188</v>
+        <v>2038</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -10331,15 +10331,15 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J138">
-        <v>747</v>
+        <v>735</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851452</t>
+          <t xml:space="preserve">311851447</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10406,11 +10406,11 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J139">
-        <v>431</v>
+        <v>735</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -10481,11 +10481,11 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J140">
-        <v>2038</v>
+        <v>1010</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -10556,11 +10556,11 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J141">
-        <v>735</v>
+        <v>385</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -10631,11 +10631,11 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J142">
-        <v>735</v>
+        <v>379</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
@@ -10691,30 +10691,30 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 108</t>
+          <t xml:space="preserve">Hovedgaden 42</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4350</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">7226325</t>
+          <t xml:space="preserve">2410274</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J143">
-        <v>1010</v>
+        <v>3739</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851447</t>
+          <t xml:space="preserve">311852051</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-26</t>
+          <t xml:space="preserve">2035-08-28</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,30 +10766,30 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 108</t>
+          <t xml:space="preserve">Hovedgaden 42</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4350</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">7226325</t>
+          <t xml:space="preserve">7564740</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J144">
-        <v>385</v>
+        <v>640</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851447</t>
+          <t xml:space="preserve">311852047</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-26</t>
+          <t xml:space="preserve">2035-08-28</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,30 +10841,30 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 108</t>
+          <t xml:space="preserve">Højgårdsvej 23</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4350</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">7226325</t>
+          <t xml:space="preserve">7564740</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J145">
-        <v>379</v>
+        <v>261</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851447</t>
+          <t xml:space="preserve">311852046</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-26</t>
+          <t xml:space="preserve">2035-08-28</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,30 +10916,30 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 42</t>
+          <t xml:space="preserve">Tølløsevej 64</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">4350</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2410274</t>
+          <t xml:space="preserve">7376334</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J146">
-        <v>3739</v>
+        <v>1242</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852051</t>
+          <t xml:space="preserve">311852541</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-28</t>
+          <t xml:space="preserve">2035-08-29</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10991,30 +10991,30 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 42</t>
+          <t xml:space="preserve">Gl Ringstedvej 32</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">4350</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">7564740</t>
+          <t xml:space="preserve">5339867</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J147">
-        <v>640</v>
+        <v>487</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852047</t>
+          <t xml:space="preserve">311852735</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-28</t>
+          <t xml:space="preserve">2035-09-01</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,30 +11066,30 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højgårdsvej 23</t>
+          <t xml:space="preserve">Gl Ringstedvej 32</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">4350</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">7564740</t>
+          <t xml:space="preserve">5339867</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J148">
-        <v>261</v>
+        <v>348</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852046</t>
+          <t xml:space="preserve">311852735</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-28</t>
+          <t xml:space="preserve">2035-09-01</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,30 +11141,30 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tølløsevej 64</t>
+          <t xml:space="preserve">Gl Ringstedvej 32</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">7376334</t>
+          <t xml:space="preserve">5339867</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J149">
-        <v>1242</v>
+        <v>429</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852541</t>
+          <t xml:space="preserve">311852735</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-29</t>
+          <t xml:space="preserve">2035-09-01</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11231,11 +11231,11 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J150">
-        <v>487</v>
+        <v>396</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -11306,11 +11306,11 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J151">
-        <v>348</v>
+        <v>439</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -11381,11 +11381,11 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J152">
-        <v>429</v>
+        <v>396</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
@@ -11456,11 +11456,11 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J153">
-        <v>396</v>
+        <v>1293</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
@@ -11531,11 +11531,11 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J154">
-        <v>439</v>
+        <v>251</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Ringstedvej 32</t>
+          <t xml:space="preserve">Peder Billesvej 57</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11606,11 +11606,11 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J155">
-        <v>396</v>
+        <v>579</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Ringstedvej 32</t>
+          <t xml:space="preserve">Anders Larsensvej 1</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11676,20 +11676,20 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339867</t>
+          <t xml:space="preserve">8285343</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J156">
-        <v>1293</v>
+        <v>1404</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852735</t>
+          <t xml:space="preserve">311864985</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-01</t>
+          <t xml:space="preserve">2035-10-29</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Ringstedvej 32</t>
+          <t xml:space="preserve">Anders Larsensvej 3</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11751,20 +11751,20 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339867</t>
+          <t xml:space="preserve">8285343</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J157">
-        <v>251</v>
+        <v>324</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852735</t>
+          <t xml:space="preserve">311864983</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-01</t>
+          <t xml:space="preserve">2035-10-29</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peder Billesvej 57</t>
+          <t xml:space="preserve">Anders Larsensvej 5</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11826,20 +11826,20 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339867</t>
+          <t xml:space="preserve">8285343</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J158">
-        <v>579</v>
+        <v>2398</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852735</t>
+          <t xml:space="preserve">311864985</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-01</t>
+          <t xml:space="preserve">2035-10-29</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anders Larsensvej 1</t>
+          <t xml:space="preserve">Damvej 19B</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11901,20 +11901,20 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">8285343</t>
+          <t xml:space="preserve">719717, 2384607</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J159">
-        <v>1404</v>
+        <v>1096</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864985</t>
+          <t xml:space="preserve">311865044</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11966,30 +11966,30 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anders Larsensvej 3</t>
+          <t xml:space="preserve">Sportsvej 3</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">8285343</t>
+          <t xml:space="preserve">7376333</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J160">
-        <v>324</v>
+        <v>2665</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864983</t>
+          <t xml:space="preserve">311864976</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -12041,30 +12041,30 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anders Larsensvej 5</t>
+          <t xml:space="preserve">Sportsvej 3</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">8285343</t>
+          <t xml:space="preserve">7376333</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J161">
-        <v>2398</v>
+        <v>2066</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864985</t>
+          <t xml:space="preserve">311864976</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12116,30 +12116,30 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damvej 19B</t>
+          <t xml:space="preserve">Sportsvej 3</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">719717, 2384607</t>
+          <t xml:space="preserve">7376333</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J162">
-        <v>1096</v>
+        <v>1115</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865044</t>
+          <t xml:space="preserve">311864976</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12206,15 +12206,15 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J163">
-        <v>2665</v>
+        <v>466</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864976</t>
+          <t xml:space="preserve">311864978</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12266,30 +12266,30 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 3</t>
+          <t xml:space="preserve">Vandtårnsvej 10</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">7376333</t>
+          <t xml:space="preserve">5339264</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J164">
-        <v>2066</v>
+        <v>2285</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864976</t>
+          <t xml:space="preserve">311865119</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12341,30 +12341,30 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 3</t>
+          <t xml:space="preserve">Vandtårnsvej 14</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">7376333</t>
+          <t xml:space="preserve">8077972</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J165">
-        <v>1115</v>
+        <v>280</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864976</t>
+          <t xml:space="preserve">311865122</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12416,30 +12416,30 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 3</t>
+          <t xml:space="preserve">Mellemvang 7</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">7376333</t>
+          <t xml:space="preserve">5340835</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J166">
-        <v>466</v>
+        <v>283</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864978</t>
+          <t xml:space="preserve">311865496</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-29</t>
+          <t xml:space="preserve">2035-10-30</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12491,40 +12491,40 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandtårnsvej 10</t>
+          <t xml:space="preserve">Brøndevej 15</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4305</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339264</t>
+          <t xml:space="preserve">719735, 2395810</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J167">
-        <v>2285</v>
+        <v>1542</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865121</t>
+          <t xml:space="preserve">311865658</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CB Group ApS</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-29</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandtårnsvej 14</t>
+          <t xml:space="preserve">Parallelvej 52</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12576,20 +12576,20 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">8077972</t>
+          <t xml:space="preserve">5335410</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J168">
-        <v>280</v>
+        <v>739</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865122</t>
+          <t xml:space="preserve">311866225</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-29</t>
+          <t xml:space="preserve">2035-11-04</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemvang 7</t>
+          <t xml:space="preserve">Parallelvej 52</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12651,20 +12651,20 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340835</t>
+          <t xml:space="preserve">5335410</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J169">
-        <v>283</v>
+        <v>640</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865496</t>
+          <t xml:space="preserve">311866227</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-30</t>
+          <t xml:space="preserve">2035-11-04</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12716,30 +12716,30 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndevej 15</t>
+          <t xml:space="preserve">Skamstrupvej 18</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">4305</t>
+          <t xml:space="preserve">4440</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">719735, 2395810</t>
+          <t xml:space="preserve">2391265</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J170">
-        <v>1542</v>
+        <v>1511</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865658</t>
+          <t xml:space="preserve">311866718</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-31</t>
+          <t xml:space="preserve">2035-11-06</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12791,30 +12791,30 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 52</t>
+          <t xml:space="preserve">Skamstrupvej 18</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4440</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335410</t>
+          <t xml:space="preserve">2391265</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J171">
-        <v>739</v>
+        <v>1990</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866225</t>
+          <t xml:space="preserve">311866718</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-04</t>
+          <t xml:space="preserve">2035-11-06</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12866,30 +12866,30 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 52</t>
+          <t xml:space="preserve">Skamstrupvej 18</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4440</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335410</t>
+          <t xml:space="preserve">2391265</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J172">
-        <v>640</v>
+        <v>796</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866227</t>
+          <t xml:space="preserve">311866718</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-04</t>
+          <t xml:space="preserve">2035-11-06</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12956,11 +12956,11 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J173">
-        <v>1511</v>
+        <v>836</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -13016,30 +13016,30 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skamstrupvej 18</t>
+          <t xml:space="preserve">Østergårdsvej 49</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">4440</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391265</t>
+          <t xml:space="preserve">2402461</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J174">
-        <v>1990</v>
+        <v>1804</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866718</t>
+          <t xml:space="preserve">311867558</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-06</t>
+          <t xml:space="preserve">2035-11-11</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13091,30 +13091,30 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skamstrupvej 18</t>
+          <t xml:space="preserve">Østergårdsvej 51A</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">4440</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391265</t>
+          <t xml:space="preserve">2402461</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J175">
-        <v>796</v>
+        <v>280</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866718</t>
+          <t xml:space="preserve">311867559</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-06</t>
+          <t xml:space="preserve">2035-11-11</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13166,30 +13166,30 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skamstrupvej 18</t>
+          <t xml:space="preserve">Østergårdsvej 53A</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">4440</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391265</t>
+          <t xml:space="preserve">8820316</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J176">
-        <v>836</v>
+        <v>729</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866718</t>
+          <t xml:space="preserve">311867560</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-06</t>
+          <t xml:space="preserve">2035-11-11</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13241,30 +13241,30 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergårdsvej 49</t>
+          <t xml:space="preserve">Bygaden 50</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4305</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402461</t>
+          <t xml:space="preserve">2395798</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J177">
-        <v>1804</v>
+        <v>467</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867558</t>
+          <t xml:space="preserve">311867756</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-11</t>
+          <t xml:space="preserve">2035-11-12</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13316,30 +13316,30 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergårdsvej 51A</t>
+          <t xml:space="preserve">Orø Havn 3</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4305</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402461</t>
+          <t xml:space="preserve">2395790</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J178">
-        <v>280</v>
+        <v>452</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867559</t>
+          <t xml:space="preserve">311868836</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-11</t>
+          <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13391,17 +13391,17 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergårdsvej 53A</t>
+          <t xml:space="preserve">Krogvejen 4</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">8820316</t>
+          <t xml:space="preserve">2397479</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -13410,11 +13410,11 @@
         </is>
       </c>
       <c r="J179">
-        <v>729</v>
+        <v>427</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867560</t>
+          <t xml:space="preserve">311872573</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-11</t>
+          <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13466,30 +13466,30 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 50</t>
+          <t xml:space="preserve">Krogvejen 4</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">4305</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395798</t>
+          <t xml:space="preserve">2397479</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J180">
-        <v>467</v>
+        <v>645</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867756</t>
+          <t xml:space="preserve">311872573</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13499,7 +13499,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-12</t>
+          <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13541,30 +13541,30 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orø Havn 3</t>
+          <t xml:space="preserve">Krogvejen 4</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">4305</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395790</t>
+          <t xml:space="preserve">2397479</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J181">
-        <v>452</v>
+        <v>320</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868836</t>
+          <t xml:space="preserve">311872573</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-18</t>
+          <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13631,11 +13631,11 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J182">
-        <v>427</v>
+        <v>1402</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
@@ -13706,15 +13706,15 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J183">
-        <v>645</v>
+        <v>290</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872573</t>
+          <t xml:space="preserve">311872576</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13766,30 +13766,30 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogvejen 4</t>
+          <t xml:space="preserve">Stestrupvej 41A</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4360</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2397479</t>
+          <t xml:space="preserve">2400079, 100800056</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J184">
-        <v>320</v>
+        <v>1084</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872573</t>
+          <t xml:space="preserve">311874431</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-09</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13841,30 +13841,30 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogvejen 4</t>
+          <t xml:space="preserve">Stestrupvej 41B</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4360</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2397479</t>
+          <t xml:space="preserve">2400080, 100800076</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J185">
-        <v>1402</v>
+        <v>1469</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872573</t>
+          <t xml:space="preserve">311874432</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-09</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13916,30 +13916,30 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogvejen 4</t>
+          <t xml:space="preserve">Hesseløvej 12</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2397479</t>
+          <t xml:space="preserve">7153439</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J186">
-        <v>290</v>
+        <v>960</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872576</t>
+          <t xml:space="preserve">311875725</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-09</t>
+          <t xml:space="preserve">2036-01-08</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13991,30 +13991,30 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stestrupvej 41A</t>
+          <t xml:space="preserve">Kalvemosevej 1</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">4360</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2400079, 100800056</t>
+          <t xml:space="preserve">100459791</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J187">
-        <v>1084</v>
+        <v>379</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874431</t>
+          <t xml:space="preserve">311880095</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-19</t>
+          <t xml:space="preserve">2036-02-03</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14066,40 +14066,40 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stestrupvej 41B</t>
+          <t xml:space="preserve">Hovedgaden 36A</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">4360</t>
+          <t xml:space="preserve">4420</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2400080, 100800076</t>
+          <t xml:space="preserve">2402019</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J188">
-        <v>1469</v>
+        <v>348</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874429</t>
+          <t xml:space="preserve">311882274</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve">CB Group ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-19</t>
+          <t xml:space="preserve">2036-02-16</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14141,17 +14141,17 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hesseløvej 12</t>
+          <t xml:space="preserve">Hovedgaden 36A</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4420</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">7153439</t>
+          <t xml:space="preserve">2402027</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -14160,11 +14160,11 @@
         </is>
       </c>
       <c r="J189">
-        <v>960</v>
+        <v>879</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875725</t>
+          <t xml:space="preserve">311882268</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-08</t>
+          <t xml:space="preserve">2036-02-16</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14216,40 +14216,40 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalvemosevej 1</t>
+          <t xml:space="preserve">Hovedgaden 36A</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4420</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">100459791</t>
+          <t xml:space="preserve">2402027</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J190">
-        <v>379</v>
+        <v>348</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880095</t>
+          <t xml:space="preserve">311882275</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t xml:space="preserve">CB Group ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-03</t>
+          <t xml:space="preserve">2036-02-16</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 36A</t>
+          <t xml:space="preserve">Hovedgaden 36B</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -14301,25 +14301,25 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402019</t>
+          <t xml:space="preserve">2402030</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J191">
-        <v>348</v>
+        <v>445</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882274</t>
+          <t xml:space="preserve">311882265</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CB Group ApS</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 36A</t>
+          <t xml:space="preserve">Hovedgaden 36B</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -14376,25 +14376,25 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402027</t>
+          <t xml:space="preserve">2402030</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J192">
-        <v>879</v>
+        <v>592</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882268</t>
+          <t xml:space="preserve">311882266</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t xml:space="preserve">CB Group ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -14441,40 +14441,40 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 36A</t>
+          <t xml:space="preserve">Kalvemosevej 3</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">4420</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402027</t>
+          <t xml:space="preserve">5340919</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J193">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882275</t>
+          <t xml:space="preserve">311882720</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CB Group ApS</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-16</t>
+          <t xml:space="preserve">2036-02-18</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14516,30 +14516,30 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 36B</t>
+          <t xml:space="preserve">Kalvemosevej 3</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">4420</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402030</t>
+          <t xml:space="preserve">5340919</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J194">
-        <v>445</v>
+        <v>640</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882265</t>
+          <t xml:space="preserve">311882720</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-16</t>
+          <t xml:space="preserve">2036-02-18</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14591,40 +14591,40 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 36B</t>
+          <t xml:space="preserve">Stestrupvej 49</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">4420</t>
+          <t xml:space="preserve">4360</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402030</t>
+          <t xml:space="preserve">8921449</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J195">
-        <v>592</v>
+        <v>3302</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882266</t>
+          <t xml:space="preserve">311888237</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CB Group ApS</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-16</t>
+          <t xml:space="preserve">2036-03-18</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14666,30 +14666,30 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalvemosevej 3</t>
+          <t xml:space="preserve">Stestrupvej 49</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4360</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340919</t>
+          <t xml:space="preserve">8921449</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J196">
-        <v>345</v>
+        <v>455</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882720</t>
+          <t xml:space="preserve">311888240</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-18</t>
+          <t xml:space="preserve">2036-03-18</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14741,30 +14741,30 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalvemosevej 3</t>
+          <t xml:space="preserve">Holbækvej 36</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4370</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340919</t>
+          <t xml:space="preserve">9167622</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J197">
-        <v>640</v>
+        <v>1082</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882720</t>
+          <t xml:space="preserve">311893637</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-18</t>
+          <t xml:space="preserve">2036-04-13</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14816,30 +14816,30 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stestrupvej 49</t>
+          <t xml:space="preserve">Bøgen 1</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">4360</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">8921449</t>
+          <t xml:space="preserve">719732, 5336412</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J198">
-        <v>3302</v>
+        <v>632</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888237</t>
+          <t xml:space="preserve">311898603</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14849,7 +14849,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-18</t>
+          <t xml:space="preserve">2036-05-04</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14891,30 +14891,30 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stestrupvej 49</t>
+          <t xml:space="preserve">Holbækvej 30C</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">4360</t>
+          <t xml:space="preserve">4370</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">8921449</t>
+          <t xml:space="preserve">2408102</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J199">
-        <v>455</v>
+        <v>1080</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888240</t>
+          <t xml:space="preserve">311904052</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-18</t>
+          <t xml:space="preserve">2036-05-27</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 36</t>
+          <t xml:space="preserve">Holbækvej 34</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -14976,20 +14976,20 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">9167622</t>
+          <t xml:space="preserve">719778, 2408102</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J200">
-        <v>1082</v>
+        <v>2048</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893637</t>
+          <t xml:space="preserve">311904037</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-13</t>
+          <t xml:space="preserve">2036-05-27</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15041,30 +15041,30 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgen 1</t>
+          <t xml:space="preserve">Hovedgaden 74</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4520</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">719732, 5336412</t>
+          <t xml:space="preserve">2391620</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J201">
-        <v>632</v>
+        <v>722</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898603</t>
+          <t xml:space="preserve">311903997</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -15074,7 +15074,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-04</t>
+          <t xml:space="preserve">2036-05-27</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -15116,30 +15116,30 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 30C</t>
+          <t xml:space="preserve">Hovedgaden 74</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">4370</t>
+          <t xml:space="preserve">4520</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408102</t>
+          <t xml:space="preserve">2391620</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J202">
-        <v>1080</v>
+        <v>640</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311904052</t>
+          <t xml:space="preserve">311903995</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15191,30 +15191,30 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 34</t>
+          <t xml:space="preserve">Hovedgaden 76F</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">4370</t>
+          <t xml:space="preserve">4520</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">719778, 2408102</t>
+          <t xml:space="preserve">2391620</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J203">
-        <v>2048</v>
+        <v>441</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311904037</t>
+          <t xml:space="preserve">311903995</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15266,7 +15266,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 74</t>
+          <t xml:space="preserve">Hovedgaden 76F</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -15281,15 +15281,15 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J204">
-        <v>722</v>
+        <v>654</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903997</t>
+          <t xml:space="preserve">311903995</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 74</t>
+          <t xml:space="preserve">Hovedgaden 76F</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -15356,11 +15356,11 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J205">
-        <v>640</v>
+        <v>4699</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
@@ -15431,11 +15431,11 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J206">
-        <v>441</v>
+        <v>622</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
@@ -15491,30 +15491,30 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 76F</t>
+          <t xml:space="preserve">Hybenvang 61A</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">4520</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391620</t>
+          <t xml:space="preserve">265333, 265334</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J207">
-        <v>654</v>
+        <v>418</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903995</t>
+          <t xml:space="preserve">311904008</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15566,30 +15566,30 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 76F</t>
+          <t xml:space="preserve">Hybenvang 63</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">4520</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391620</t>
+          <t xml:space="preserve">5340689</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J208">
-        <v>4699</v>
+        <v>634</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903995</t>
+          <t xml:space="preserve">311904029</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -15641,30 +15641,30 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 76F</t>
+          <t xml:space="preserve">Nygade 9</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">4520</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391620</t>
+          <t xml:space="preserve">7618119</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J209">
-        <v>622</v>
+        <v>4058</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903995</t>
+          <t xml:space="preserve">311905846</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -15674,7 +15674,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-27</t>
+          <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hybenvang 61A</t>
+          <t xml:space="preserve">Nygade 9</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -15726,20 +15726,20 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">265333, 265334</t>
+          <t xml:space="preserve">7618119</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J210">
-        <v>418</v>
+        <v>382</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311904008</t>
+          <t xml:space="preserve">311905846</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-27</t>
+          <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15791,17 +15791,17 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hybenvang 63</t>
+          <t xml:space="preserve">Holbækvej 30B</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4370</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340689</t>
+          <t xml:space="preserve">2408076</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -15810,11 +15810,11 @@
         </is>
       </c>
       <c r="J211">
-        <v>634</v>
+        <v>2062</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311904029</t>
+          <t xml:space="preserve">311909485</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15824,7 +15824,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-27</t>
+          <t xml:space="preserve">2036-06-19</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15866,30 +15866,30 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 9</t>
+          <t xml:space="preserve">Holbækvej 30F</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4370</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">7618119</t>
+          <t xml:space="preserve">2408076</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J212">
-        <v>4058</v>
+        <v>376</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905846</t>
+          <t xml:space="preserve">311909486</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15899,7 +15899,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-04</t>
+          <t xml:space="preserve">2036-06-19</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 9</t>
+          <t xml:space="preserve">Udby Kirkevej 25</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -15951,20 +15951,20 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">7618119</t>
+          <t xml:space="preserve">7960027</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J213">
-        <v>382</v>
+        <v>519</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905846</t>
+          <t xml:space="preserve">311910894</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-04</t>
+          <t xml:space="preserve">2036-06-25</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -16016,30 +16016,30 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 30B</t>
+          <t xml:space="preserve">Kasernevej 43</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">4370</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408076</t>
+          <t xml:space="preserve">7095821</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J214">
-        <v>2062</v>
+        <v>802</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311909485</t>
+          <t xml:space="preserve">311911466</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-19</t>
+          <t xml:space="preserve">2036-06-29</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -16091,30 +16091,30 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 30F</t>
+          <t xml:space="preserve">Kasernevej 43</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">4370</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408076</t>
+          <t xml:space="preserve">7095821</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J215">
-        <v>376</v>
+        <v>1348</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311909486</t>
+          <t xml:space="preserve">311911466</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-19</t>
+          <t xml:space="preserve">2036-06-29</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -16166,30 +16166,30 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udby Kirkevej 25</t>
+          <t xml:space="preserve">Sportsvej 5</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">7960027</t>
+          <t xml:space="preserve">7376333</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J216">
-        <v>519</v>
+        <v>352</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311910894</t>
+          <t xml:space="preserve">311911482</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-25</t>
+          <t xml:space="preserve">2036-06-29</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kasernevej 43</t>
+          <t xml:space="preserve">Torpet 1</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -16251,20 +16251,20 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">7095821</t>
+          <t xml:space="preserve">10218277</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J217">
-        <v>802</v>
+        <v>1088</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911471</t>
+          <t xml:space="preserve">311911479</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16316,40 +16316,40 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kasernevej 43</t>
+          <t xml:space="preserve">Rensdyrvej 2</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">7095821</t>
+          <t xml:space="preserve">2399272</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J218">
-        <v>1348</v>
+        <v>5665</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911466</t>
+          <t xml:space="preserve">311911823</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t xml:space="preserve">CB Group ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-29</t>
+          <t xml:space="preserve">2036-06-30</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -16391,40 +16391,40 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 5</t>
+          <t xml:space="preserve">Rensdyrvej 4</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">7376333</t>
+          <t xml:space="preserve">2399272</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J219">
-        <v>352</v>
+        <v>1315</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911482</t>
+          <t xml:space="preserve">311911823</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t xml:space="preserve">CB Group ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-29</t>
+          <t xml:space="preserve">2036-06-30</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -16466,40 +16466,40 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torpet 1</t>
+          <t xml:space="preserve">Rensdyrvej 4</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">10218277</t>
+          <t xml:space="preserve">2399272</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J220">
-        <v>1088</v>
+        <v>1277</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911479</t>
+          <t xml:space="preserve">311911823</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t xml:space="preserve">CB Group ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-29</t>
+          <t xml:space="preserve">2036-06-30</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -16541,40 +16541,40 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rensdyrvej 2</t>
+          <t xml:space="preserve">Tuse Byvej 16</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399272</t>
+          <t xml:space="preserve">2393534</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J221">
-        <v>5665</v>
+        <v>2664</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911823</t>
+          <t xml:space="preserve">311912618</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CB Group ApS</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-30</t>
+          <t xml:space="preserve">2036-07-03</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16616,30 +16616,30 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rensdyrvej 4</t>
+          <t xml:space="preserve">Tuse Byvej 16</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399272</t>
+          <t xml:space="preserve">2393534</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J222">
-        <v>1315</v>
+        <v>673</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911826</t>
+          <t xml:space="preserve">311912618</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -16649,7 +16649,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-30</t>
+          <t xml:space="preserve">2036-07-03</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16691,30 +16691,30 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rensdyrvej 4</t>
+          <t xml:space="preserve">Tølløsevej 58</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399272</t>
+          <t xml:space="preserve">2409847</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J223">
-        <v>1277</v>
+        <v>401</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911826</t>
+          <t xml:space="preserve">311916428</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-30</t>
+          <t xml:space="preserve">2036-07-29</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16766,30 +16766,30 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 16</t>
+          <t xml:space="preserve">Tølløsevej 58</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393534</t>
+          <t xml:space="preserve">2409847</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J224">
-        <v>2664</v>
+        <v>357</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311912618</t>
+          <t xml:space="preserve">311916427</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -16799,7 +16799,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-03</t>
+          <t xml:space="preserve">2036-07-29</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16841,30 +16841,30 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 16</t>
+          <t xml:space="preserve">Tølløsevej 58</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393534</t>
+          <t xml:space="preserve">2409847</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J225">
-        <v>673</v>
+        <v>506</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311912618</t>
+          <t xml:space="preserve">311916426</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-03</t>
+          <t xml:space="preserve">2036-07-29</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16931,15 +16931,15 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J226">
-        <v>401</v>
+        <v>978</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916428</t>
+          <t xml:space="preserve">311916424</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -16991,30 +16991,30 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tølløsevej 58</t>
+          <t xml:space="preserve">Asmindrupvej 50</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2409847</t>
+          <t xml:space="preserve">2399271</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J227">
-        <v>357</v>
+        <v>589</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916427</t>
+          <t xml:space="preserve">311917298</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-29</t>
+          <t xml:space="preserve">2036-08-04</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -17066,30 +17066,30 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tølløsevej 58</t>
+          <t xml:space="preserve">Ellebjergvej 31A</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2409847</t>
+          <t xml:space="preserve">2387969</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J228">
-        <v>506</v>
+        <v>297</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916426</t>
+          <t xml:space="preserve">311919655</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-29</t>
+          <t xml:space="preserve">2036-08-17</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -17141,30 +17141,30 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tølløsevej 58</t>
+          <t xml:space="preserve">Skovlystvej 2</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2409847</t>
+          <t xml:space="preserve">2386579</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J229">
-        <v>978</v>
+        <v>1668</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916424</t>
+          <t xml:space="preserve">311919644</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -17174,7 +17174,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-29</t>
+          <t xml:space="preserve">2036-08-17</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -17216,17 +17216,17 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asmindrupvej 50</t>
+          <t xml:space="preserve">Tuse Byvej 2</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399271</t>
+          <t xml:space="preserve">2393546</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -17235,11 +17235,11 @@
         </is>
       </c>
       <c r="J230">
-        <v>589</v>
+        <v>7356</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311917298</t>
+          <t xml:space="preserve">311919716</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-04</t>
+          <t xml:space="preserve">2036-08-17</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -17291,30 +17291,30 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ellebjergvej 31A</t>
+          <t xml:space="preserve">Tuse Byvej 2</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2387969</t>
+          <t xml:space="preserve">2393546</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J231">
-        <v>297</v>
+        <v>355</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311919655</t>
+          <t xml:space="preserve">311919716</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -17366,30 +17366,30 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovlystvej 2</t>
+          <t xml:space="preserve">Tuse Byvej 8</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2386579</t>
+          <t xml:space="preserve">2393535</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J232">
-        <v>1668</v>
+        <v>308</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311919644</t>
+          <t xml:space="preserve">311919722</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -17441,30 +17441,30 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 2</t>
+          <t xml:space="preserve">Elmegården 56</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393546</t>
+          <t xml:space="preserve">2388160</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J233">
-        <v>7356</v>
+        <v>1393</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311919716</t>
+          <t xml:space="preserve">311920764</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -17474,7 +17474,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-17</t>
+          <t xml:space="preserve">2036-08-21</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 2</t>
+          <t xml:space="preserve">Tuse Byvej 8</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -17526,20 +17526,20 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393546</t>
+          <t xml:space="preserve">2393535</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J234">
-        <v>355</v>
+        <v>2701</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311919716</t>
+          <t xml:space="preserve">311921343</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -17549,7 +17549,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-17</t>
+          <t xml:space="preserve">2036-08-25</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -17591,7 +17591,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 8</t>
+          <t xml:space="preserve">Mellemvang 9</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -17601,20 +17601,20 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393535</t>
+          <t xml:space="preserve">5340827</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J235">
-        <v>308</v>
+        <v>1983</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311919722</t>
+          <t xml:space="preserve">311927578</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -17624,7 +17624,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-17</t>
+          <t xml:space="preserve">2036-09-23</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17666,30 +17666,30 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmegården 56</t>
+          <t xml:space="preserve">Centervænget 2</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2388160</t>
+          <t xml:space="preserve">2399431</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J236">
-        <v>1393</v>
+        <v>326</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311920764</t>
+          <t xml:space="preserve">311928900</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-21</t>
+          <t xml:space="preserve">2036-09-29</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17741,30 +17741,30 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 8</t>
+          <t xml:space="preserve">Centervænget 4</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393535</t>
+          <t xml:space="preserve">2399431</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J237">
-        <v>2701</v>
+        <v>400</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311921343</t>
+          <t xml:space="preserve">311928900</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -17774,7 +17774,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-25</t>
+          <t xml:space="preserve">2036-09-29</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">

--- a/public/exports/29189447.xlsx
+++ b/public/exports/29189447.xlsx
@@ -566,26 +566,26 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændholtvej 5</t>
+          <t xml:space="preserve">Bygaden 50</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4350</t>
+          <t xml:space="preserve">4305</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2410400</t>
+          <t xml:space="preserve">2395800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J8">
-        <v>713</v>
+        <v>419</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -641,26 +641,26 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 50</t>
+          <t xml:space="preserve">Carl Reffsvej 20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">4305</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395800</t>
+          <t xml:space="preserve">5335507</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J9">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Reffsvej 20</t>
+          <t xml:space="preserve">Dragerupvej 50</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -726,16 +726,16 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335507</t>
+          <t xml:space="preserve">719610, 2398678</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J10">
-        <v>412</v>
+        <v>591</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -806,11 +806,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J11">
-        <v>591</v>
+        <v>398</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dragerupvej 50</t>
+          <t xml:space="preserve">Finsings Plads 1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -876,16 +876,16 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">719610, 2398678</t>
+          <t xml:space="preserve">719742, 9386046</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J12">
-        <v>398</v>
+        <v>339</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finsings Plads 1</t>
+          <t xml:space="preserve">Forten 10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -951,16 +951,16 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">719742, 9386046</t>
+          <t xml:space="preserve">100367073</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J13">
-        <v>339</v>
+        <v>1373</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forten 10</t>
+          <t xml:space="preserve">Forten 2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1026,16 +1026,16 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">100367073</t>
+          <t xml:space="preserve">100367074</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J14">
-        <v>1373</v>
+        <v>338</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1091,26 +1091,26 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forten 2</t>
+          <t xml:space="preserve">Jernbanevej 4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">100367074</t>
+          <t xml:space="preserve">2387376</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J15">
-        <v>338</v>
+        <v>257</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1166,26 +1166,26 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanevej 4</t>
+          <t xml:space="preserve">Jernbanevej 6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2387376</t>
+          <t xml:space="preserve">5334983</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J16">
-        <v>257</v>
+        <v>354</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanevej 6</t>
+          <t xml:space="preserve">Kanalstræde 21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1251,16 +1251,16 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334983</t>
+          <t xml:space="preserve">5334804</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J17">
-        <v>354</v>
+        <v>1813</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kanalstræde 21</t>
+          <t xml:space="preserve">Kapellanvej 4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334804</t>
+          <t xml:space="preserve">719739, 5336599</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1335,7 +1335,7 @@
         </is>
       </c>
       <c r="J18">
-        <v>1813</v>
+        <v>325</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kapellanvej 4</t>
+          <t xml:space="preserve">Mejerivangen 4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1401,16 +1401,16 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">719739, 5336599</t>
+          <t xml:space="preserve">100367074</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="J19">
-        <v>325</v>
+        <v>360</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1466,26 +1466,26 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejerivangen 4</t>
+          <t xml:space="preserve">Nordgårde 4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4520</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">100367074</t>
+          <t xml:space="preserve">719761, 2391872</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J20">
-        <v>360</v>
+        <v>328</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1541,26 +1541,26 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordgårde 4</t>
+          <t xml:space="preserve">Nyvangs Allé 1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4520</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">719761, 2391872</t>
+          <t xml:space="preserve">100367074</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="J21">
-        <v>328</v>
+        <v>451</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyvangs Allé 1</t>
+          <t xml:space="preserve">Nyvangs Allé 4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1631,11 +1631,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J22">
-        <v>451</v>
+        <v>798</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyvangs Allé 4</t>
+          <t xml:space="preserve">Traktørstien 3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1706,11 +1706,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J23">
-        <v>798</v>
+        <v>415</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Traktørstien 3</t>
+          <t xml:space="preserve">Vimmelskaftet 27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1776,16 +1776,16 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">100367074</t>
+          <t xml:space="preserve">5334883</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J24">
-        <v>415</v>
+        <v>1071</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vimmelskaftet 27</t>
+          <t xml:space="preserve">Østervænget 1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334883</t>
+          <t xml:space="preserve">100367074</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J25">
-        <v>1071</v>
+        <v>2032</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervænget 1</t>
+          <t xml:space="preserve">Højen 38</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1926,35 +1926,35 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">100367074</t>
+          <t xml:space="preserve">5336438</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J26">
-        <v>2032</v>
+        <v>2726</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve">200020593</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-09-17</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -1991,30 +1991,30 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højen 38</t>
+          <t xml:space="preserve">Holbækvej 30C</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4370</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5336438</t>
+          <t xml:space="preserve">2408102</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J27">
-        <v>2726</v>
+        <v>489</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020593</t>
+          <t xml:space="preserve">200031720</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-17</t>
+          <t xml:space="preserve">2020-05-25</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2066,40 +2066,40 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 30C</t>
+          <t xml:space="preserve">Holbækvej 108A</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4370</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408102</t>
+          <t xml:space="preserve">7226325</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J28">
-        <v>489</v>
+        <v>439</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">200031720</t>
+          <t xml:space="preserve">200042618</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-05-25</t>
+          <t xml:space="preserve">2020-12-08</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 108A</t>
+          <t xml:space="preserve">Kalundborgvej 54F</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">7226325</t>
+          <t xml:space="preserve">719616, 5339534</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2160,11 +2160,11 @@
         </is>
       </c>
       <c r="J29">
-        <v>439</v>
+        <v>671</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042632</t>
+          <t xml:space="preserve">200047054</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-08</t>
+          <t xml:space="preserve">2021-03-21</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborgvej 54F</t>
+          <t xml:space="preserve">Chr Hansensvej 11A</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2226,40 +2226,40 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">719616, 5339534</t>
+          <t xml:space="preserve">5335077</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J30">
-        <v>671</v>
+        <v>310</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047054</t>
+          <t xml:space="preserve">311218750</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-21</t>
+          <t xml:space="preserve">2026-12-20</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chr Hansensvej 11A</t>
+          <t xml:space="preserve">Tuse Byvej 26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335077</t>
+          <t xml:space="preserve">2393544</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2310,11 +2310,11 @@
         </is>
       </c>
       <c r="J31">
-        <v>310</v>
+        <v>464</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218750</t>
+          <t xml:space="preserve">311219966</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-20</t>
+          <t xml:space="preserve">2026-12-29</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 26</t>
+          <t xml:space="preserve">Tuse Byvej 42</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J32">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 42</t>
+          <t xml:space="preserve">Tuse Byvej 58</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J33">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 58</t>
+          <t xml:space="preserve">Tuse Byvej 74</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J34">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 74</t>
+          <t xml:space="preserve">Bispehøjen 4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2601,20 +2601,20 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393544</t>
+          <t xml:space="preserve">5336543</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J35">
-        <v>464</v>
+        <v>606</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219966</t>
+          <t xml:space="preserve">311220222</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-29</t>
+          <t xml:space="preserve">2027-01-02</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bispehøjen 4</t>
+          <t xml:space="preserve">Gasværksvej 9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">5336543</t>
+          <t xml:space="preserve">5334816</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2685,11 +2685,11 @@
         </is>
       </c>
       <c r="J36">
-        <v>606</v>
+        <v>1192</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220222</t>
+          <t xml:space="preserve">311220229</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasværksvej 9</t>
+          <t xml:space="preserve">Parallelvej 52</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2751,20 +2751,20 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334816</t>
+          <t xml:space="preserve">5335410</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J37">
-        <v>1192</v>
+        <v>288</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220229</t>
+          <t xml:space="preserve">311220230</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 52</t>
+          <t xml:space="preserve">Konsul Beÿers Allé 1A</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2826,20 +2826,20 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335410</t>
+          <t xml:space="preserve">8366959</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J38">
-        <v>288</v>
+        <v>509</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220230</t>
+          <t xml:space="preserve">311220673</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-02</t>
+          <t xml:space="preserve">2027-01-04</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Konsul Beÿers Allé 1A</t>
+          <t xml:space="preserve">Tuse Byvej 24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">8366959</t>
+          <t xml:space="preserve">265751, 265752</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2910,11 +2910,11 @@
         </is>
       </c>
       <c r="J39">
-        <v>509</v>
+        <v>939</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220673</t>
+          <t xml:space="preserve">311222478</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-04</t>
+          <t xml:space="preserve">2027-01-13</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2966,17 +2966,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 24</t>
+          <t xml:space="preserve">Sønderstrupvej 26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">265751, 265752</t>
+          <t xml:space="preserve">100078242</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2985,21 +2985,21 @@
         </is>
       </c>
       <c r="J40">
-        <v>939</v>
+        <v>6249</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311222478</t>
+          <t xml:space="preserve">311225362</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+          <t xml:space="preserve">John Klysner Consult ApS</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-13</t>
+          <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderstrupvej 26</t>
+          <t xml:space="preserve">Rørvangsvej 4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">100078242</t>
+          <t xml:space="preserve">5340673</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3060,21 +3060,21 @@
         </is>
       </c>
       <c r="J41">
-        <v>6249</v>
+        <v>1017</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225362</t>
+          <t xml:space="preserve">311233036</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Klysner Consult ApS</t>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-30</t>
+          <t xml:space="preserve">2027-03-09</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kasernevej 6</t>
+          <t xml:space="preserve">Karensmindevej 7</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">8033723</t>
+          <t xml:space="preserve">5335611</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3135,11 +3135,11 @@
         </is>
       </c>
       <c r="J42">
-        <v>2314</v>
+        <v>1170</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229616</t>
+          <t xml:space="preserve">311233787</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-21</t>
+          <t xml:space="preserve">2027-03-13</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rørvangsvej 4</t>
+          <t xml:space="preserve">Munkevænget 38</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340673</t>
+          <t xml:space="preserve">5336544</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3210,11 +3210,11 @@
         </is>
       </c>
       <c r="J43">
-        <v>1017</v>
+        <v>730</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233036</t>
+          <t xml:space="preserve">311233788</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-09</t>
+          <t xml:space="preserve">2027-03-13</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karensmindevej 7</t>
+          <t xml:space="preserve">Carl Reffsvej 2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335611</t>
+          <t xml:space="preserve">270089</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3285,11 +3285,11 @@
         </is>
       </c>
       <c r="J44">
-        <v>1170</v>
+        <v>2052</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233787</t>
+          <t xml:space="preserve">311234340</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-13</t>
+          <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Munkevænget 38</t>
+          <t xml:space="preserve">Carl Reffsvej 32</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3351,20 +3351,20 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5336544</t>
+          <t xml:space="preserve">5335507</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J45">
-        <v>730</v>
+        <v>306</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233788</t>
+          <t xml:space="preserve">311234425</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-13</t>
+          <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Reffsvej 2</t>
+          <t xml:space="preserve">Carl Reffsvej 42</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3426,20 +3426,20 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">270089</t>
+          <t xml:space="preserve">5335507</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J46">
-        <v>2052</v>
+        <v>1244</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234340</t>
+          <t xml:space="preserve">311234435</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Reffsvej 32</t>
+          <t xml:space="preserve">Carl Reffsvej 78</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J47">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Reffsvej 42</t>
+          <t xml:space="preserve">Carl Reffsvej 8</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3581,15 +3581,15 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J48">
-        <v>1244</v>
+        <v>412</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234435</t>
+          <t xml:space="preserve">311234425</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Reffsvej 78</t>
+          <t xml:space="preserve">Carl Reffsvej 88</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3656,15 +3656,15 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J49">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234425</t>
+          <t xml:space="preserve">311234423</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Reffsvej 8</t>
+          <t xml:space="preserve">Stenhusvej 23A</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3726,20 +3726,20 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335507</t>
+          <t xml:space="preserve">7573379</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J50">
-        <v>412</v>
+        <v>512</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234425</t>
+          <t xml:space="preserve">311236497</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-15</t>
+          <t xml:space="preserve">2027-03-24</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Reffsvej 88</t>
+          <t xml:space="preserve">Stenhusvej 25A</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3801,20 +3801,20 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335507</t>
+          <t xml:space="preserve">7573379</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J51">
-        <v>303</v>
+        <v>512</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234423</t>
+          <t xml:space="preserve">311236497</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-15</t>
+          <t xml:space="preserve">2027-03-24</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenhusvej 23A</t>
+          <t xml:space="preserve">Stenhusvej 27A</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J52">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenhusvej 25A</t>
+          <t xml:space="preserve">Stenhusvej 29A</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J53">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenhusvej 27A</t>
+          <t xml:space="preserve">Stenhusvej 31A</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J54">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenhusvej 29A</t>
+          <t xml:space="preserve">Stenhusvej 21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4101,20 +4101,20 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">7573379</t>
+          <t xml:space="preserve">271115, 271116</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J55">
-        <v>512</v>
+        <v>6192</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236497</t>
+          <t xml:space="preserve">311237694</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-24</t>
+          <t xml:space="preserve">2027-03-30</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenhusvej 31A</t>
+          <t xml:space="preserve">Gl Tuse Næs Vej 15A</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4176,20 +4176,20 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">7573379</t>
+          <t xml:space="preserve">272010, 272011</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J56">
-        <v>512</v>
+        <v>1658</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236497</t>
+          <t xml:space="preserve">311239402</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-24</t>
+          <t xml:space="preserve">2027-04-06</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenhusvej 21</t>
+          <t xml:space="preserve">Gl Tuse Næs Vej 15B</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4251,20 +4251,20 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">271115, 271116</t>
+          <t xml:space="preserve">272010</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J57">
-        <v>6192</v>
+        <v>1846</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311237694</t>
+          <t xml:space="preserve">311239403</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-30</t>
+          <t xml:space="preserve">2027-04-06</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Tuse Næs Vej 15A</t>
+          <t xml:space="preserve">Tidemandsvej 1A</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4326,25 +4326,25 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">272010, 272011</t>
+          <t xml:space="preserve">5335169</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J58">
-        <v>1658</v>
+        <v>641</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311239402</t>
+          <t xml:space="preserve">311239463</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Tuse Næs Vej 15B</t>
+          <t xml:space="preserve">Kattegatsvej 11</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4401,20 +4401,20 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">272010</t>
+          <t xml:space="preserve">8077237</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J59">
-        <v>1846</v>
+        <v>470</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311239403</t>
+          <t xml:space="preserve">311242885</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-06</t>
+          <t xml:space="preserve">2027-04-25</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tidemandsvej 1A</t>
+          <t xml:space="preserve">Jernbanevej 6</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4476,30 +4476,30 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335169</t>
+          <t xml:space="preserve">5334983</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J60">
-        <v>641</v>
+        <v>8718</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311239463</t>
+          <t xml:space="preserve">311243219</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-06</t>
+          <t xml:space="preserve">2027-04-26</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kattegatsvej 11</t>
+          <t xml:space="preserve">Rolighedsstræde 2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">8077237</t>
+          <t xml:space="preserve">5334475</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4560,11 +4560,11 @@
         </is>
       </c>
       <c r="J61">
-        <v>470</v>
+        <v>256</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242885</t>
+          <t xml:space="preserve">311243209</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-25</t>
+          <t xml:space="preserve">2027-04-26</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanevej 6</t>
+          <t xml:space="preserve">Rolighedsstræde 5</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334983</t>
+          <t xml:space="preserve">5334947</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4635,11 +4635,11 @@
         </is>
       </c>
       <c r="J62">
-        <v>8718</v>
+        <v>410</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243219</t>
+          <t xml:space="preserve">311243212</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolighedsstræde 2</t>
+          <t xml:space="preserve">Roskildevej 12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334475</t>
+          <t xml:space="preserve">7805439</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4710,16 +4710,16 @@
         </is>
       </c>
       <c r="J63">
-        <v>256</v>
+        <v>540</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243209</t>
+          <t xml:space="preserve">311243217</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4766,17 +4766,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolighedsstræde 5</t>
+          <t xml:space="preserve">Ellebjergvej 31B</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334947</t>
+          <t xml:space="preserve">100044734</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4785,21 +4785,21 @@
         </is>
       </c>
       <c r="J64">
-        <v>410</v>
+        <v>615</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243212</t>
+          <t xml:space="preserve">311248907</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-26</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4841,17 +4841,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskildevej 12</t>
+          <t xml:space="preserve">Hjortholmvej 9A</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">7805439</t>
+          <t xml:space="preserve">2409849</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4860,11 +4860,11 @@
         </is>
       </c>
       <c r="J65">
-        <v>540</v>
+        <v>1876</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243217</t>
+          <t xml:space="preserve">311248975</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-26</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4916,17 +4916,17 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ellebjergvej 31B</t>
+          <t xml:space="preserve">Kikhøjparken 1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">100044734</t>
+          <t xml:space="preserve">5339293</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4935,11 +4935,11 @@
         </is>
       </c>
       <c r="J66">
-        <v>615</v>
+        <v>1227</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248907</t>
+          <t xml:space="preserve">311249402</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-05-23</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4991,17 +4991,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjortholmvej 9A</t>
+          <t xml:space="preserve">Blomstervænget 2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4420</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2409849</t>
+          <t xml:space="preserve">7637708</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5010,21 +5010,21 @@
         </is>
       </c>
       <c r="J67">
-        <v>1876</v>
+        <v>872</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248975</t>
+          <t xml:space="preserve">311250302</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-05-29</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,17 +5066,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kikhøjparken 1</t>
+          <t xml:space="preserve">Byparken 2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4520</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339293</t>
+          <t xml:space="preserve">2392048</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5085,11 +5085,11 @@
         </is>
       </c>
       <c r="J68">
-        <v>1227</v>
+        <v>1053</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311249402</t>
+          <t xml:space="preserve">311251071</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-23</t>
+          <t xml:space="preserve">2027-05-31</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blomstervænget 2</t>
+          <t xml:space="preserve">Gl. Skovvej 150C</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">7637708</t>
+          <t xml:space="preserve">2401337</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5160,11 +5160,11 @@
         </is>
       </c>
       <c r="J69">
-        <v>872</v>
+        <v>1128</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311250302</t>
+          <t xml:space="preserve">311251192</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-29</t>
+          <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5216,30 +5216,30 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byparken 2</t>
+          <t xml:space="preserve">Gl. Skovvej 150C</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4520</t>
+          <t xml:space="preserve">4420</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2392048</t>
+          <t xml:space="preserve">2401337</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J70">
-        <v>1053</v>
+        <v>1731</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251071</t>
+          <t xml:space="preserve">311251192</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-31</t>
+          <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5306,11 +5306,11 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J71">
-        <v>1128</v>
+        <v>2223</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -5381,11 +5381,11 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J72">
-        <v>1731</v>
+        <v>795</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -5441,30 +5441,30 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Skovvej 150C</t>
+          <t xml:space="preserve">Damvej 14A</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">4420</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2401337</t>
+          <t xml:space="preserve">2384645</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J73">
-        <v>2223</v>
+        <v>799</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251192</t>
+          <t xml:space="preserve">311251899</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-01</t>
+          <t xml:space="preserve">2027-06-06</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5516,30 +5516,30 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Skovvej 150C</t>
+          <t xml:space="preserve">Damvej 14B</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">4420</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2401337</t>
+          <t xml:space="preserve">2384645</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J74">
-        <v>795</v>
+        <v>439</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251192</t>
+          <t xml:space="preserve">311251898</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-01</t>
+          <t xml:space="preserve">2027-06-06</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5591,30 +5591,30 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damvej 14A</t>
+          <t xml:space="preserve">Holløsevej 10C</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4420</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2384645</t>
+          <t xml:space="preserve">2401302</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J75">
-        <v>799</v>
+        <v>564</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251899</t>
+          <t xml:space="preserve">311258791</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5666,30 +5666,30 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damvej 14B</t>
+          <t xml:space="preserve">Hovedgaden 40</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2384645</t>
+          <t xml:space="preserve">9415784</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J76">
-        <v>439</v>
+        <v>1014</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251898</t>
+          <t xml:space="preserve">311258739</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5741,17 +5741,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holløsevej 10C</t>
+          <t xml:space="preserve">Hovedgaden 59</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">4420</t>
+          <t xml:space="preserve">4520</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2401302</t>
+          <t xml:space="preserve">2391781</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5760,11 +5760,11 @@
         </is>
       </c>
       <c r="J77">
-        <v>564</v>
+        <v>999</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258791</t>
+          <t xml:space="preserve">311258737</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 40</t>
+          <t xml:space="preserve">Jernbanevej 18E</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5826,20 +5826,20 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">9415784</t>
+          <t xml:space="preserve">2408920</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J78">
-        <v>1014</v>
+        <v>754</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258739</t>
+          <t xml:space="preserve">311258825</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5891,17 +5891,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 59</t>
+          <t xml:space="preserve">Nytorv 14</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">4520</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391781</t>
+          <t xml:space="preserve">2408839</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5910,11 +5910,11 @@
         </is>
       </c>
       <c r="J79">
-        <v>999</v>
+        <v>840</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258737</t>
+          <t xml:space="preserve">311264148</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-08-02</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5966,17 +5966,17 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanevej 18E</t>
+          <t xml:space="preserve">Svinningehallen 1</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4520</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408920</t>
+          <t xml:space="preserve">719759, 2391621</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5985,11 +5985,11 @@
         </is>
       </c>
       <c r="J80">
-        <v>754</v>
+        <v>3125</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258825</t>
+          <t xml:space="preserve">311350102</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-05</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nytorv 14</t>
+          <t xml:space="preserve">Øvej 5A</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408839</t>
+          <t xml:space="preserve">2402709</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6060,11 +6060,11 @@
         </is>
       </c>
       <c r="J81">
-        <v>840</v>
+        <v>1724</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264148</t>
+          <t xml:space="preserve">311272027</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-02</t>
+          <t xml:space="preserve">2027-09-11</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6116,30 +6116,30 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svinningehallen 1</t>
+          <t xml:space="preserve">Øvej 5B</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">4520</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">719759, 2391621</t>
+          <t xml:space="preserve">2402709</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J82">
-        <v>3125</v>
+        <v>346</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311350102</t>
+          <t xml:space="preserve">311272304</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-05</t>
+          <t xml:space="preserve">2027-09-12</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6191,17 +6191,17 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øvej 5A</t>
+          <t xml:space="preserve">Markedspladsen 6A</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402709</t>
+          <t xml:space="preserve">5334610</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -6210,11 +6210,11 @@
         </is>
       </c>
       <c r="J83">
-        <v>1724</v>
+        <v>472</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272027</t>
+          <t xml:space="preserve">311274663</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-11</t>
+          <t xml:space="preserve">2027-09-22</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øvej 5B</t>
+          <t xml:space="preserve">Sportsvej 2</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6276,20 +6276,20 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402709</t>
+          <t xml:space="preserve">719772, 2409825</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J84">
-        <v>346</v>
+        <v>2306</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272304</t>
+          <t xml:space="preserve">311276692</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-12</t>
+          <t xml:space="preserve">2027-10-04</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6341,17 +6341,17 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Markedspladsen 6A</t>
+          <t xml:space="preserve">Østergade 64</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334610</t>
+          <t xml:space="preserve">2408814</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -6360,11 +6360,11 @@
         </is>
       </c>
       <c r="J85">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311274663</t>
+          <t xml:space="preserve">311276699</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-22</t>
+          <t xml:space="preserve">2027-10-04</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 2</t>
+          <t xml:space="preserve">Øvej 3</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6426,20 +6426,20 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">719772, 2409825</t>
+          <t xml:space="preserve">9415784</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J86">
-        <v>2306</v>
+        <v>1030</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276692</t>
+          <t xml:space="preserve">311276724</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 64</t>
+          <t xml:space="preserve">Øvej 3</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6501,20 +6501,20 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408814</t>
+          <t xml:space="preserve">9415784</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J87">
-        <v>459</v>
+        <v>1350</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276699</t>
+          <t xml:space="preserve">311276724</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6581,11 +6581,11 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J88">
-        <v>1030</v>
+        <v>820</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -6641,30 +6641,30 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øvej 3</t>
+          <t xml:space="preserve">Ledegårdsvej 15</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4520</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">9415784</t>
+          <t xml:space="preserve">2391684</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J89">
-        <v>1350</v>
+        <v>278</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276724</t>
+          <t xml:space="preserve">311281139</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-04</t>
+          <t xml:space="preserve">2027-10-30</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6716,30 +6716,30 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øvej 3</t>
+          <t xml:space="preserve">Stormøllevej 9</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">9415784</t>
+          <t xml:space="preserve">5337399</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J90">
-        <v>820</v>
+        <v>492</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276724</t>
+          <t xml:space="preserve">311282530</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-04</t>
+          <t xml:space="preserve">2027-11-07</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ledegårdsvej 15</t>
+          <t xml:space="preserve">Ved Faurgården 7</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">4520</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391684</t>
+          <t xml:space="preserve">5340353</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6810,11 +6810,11 @@
         </is>
       </c>
       <c r="J91">
-        <v>278</v>
+        <v>745</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311281139</t>
+          <t xml:space="preserve">311282521</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-30</t>
+          <t xml:space="preserve">2027-11-07</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6866,17 +6866,17 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stormøllevej 9</t>
+          <t xml:space="preserve">Industrivej 14B</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5337399</t>
+          <t xml:space="preserve">2409959</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6885,11 +6885,11 @@
         </is>
       </c>
       <c r="J92">
-        <v>492</v>
+        <v>623</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282530</t>
+          <t xml:space="preserve">311283082</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-07</t>
+          <t xml:space="preserve">2027-11-09</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6941,17 +6941,17 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Faurgården 7</t>
+          <t xml:space="preserve">Kirkevej 1</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4532</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340353</t>
+          <t xml:space="preserve">2384014</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6960,11 +6960,11 @@
         </is>
       </c>
       <c r="J93">
-        <v>745</v>
+        <v>264</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282521</t>
+          <t xml:space="preserve">311283182</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-07</t>
+          <t xml:space="preserve">2027-11-09</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7016,30 +7016,30 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 14B</t>
+          <t xml:space="preserve">Kirkevej 1</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4532</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2409959</t>
+          <t xml:space="preserve">2384014</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J94">
-        <v>623</v>
+        <v>400</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283082</t>
+          <t xml:space="preserve">311283182</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7106,11 +7106,11 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J95">
-        <v>264</v>
+        <v>553</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -7166,30 +7166,30 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 1</t>
+          <t xml:space="preserve">Ringstedvej 43A</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">4532</t>
+          <t xml:space="preserve">4440</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2384014</t>
+          <t xml:space="preserve">2390836</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J96">
-        <v>400</v>
+        <v>262</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283182</t>
+          <t xml:space="preserve">311283188</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-09</t>
+          <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7241,30 +7241,30 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 1</t>
+          <t xml:space="preserve">Skarridsøgade 37</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4532</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2384014</t>
+          <t xml:space="preserve">2388022</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J97">
-        <v>553</v>
+        <v>2632</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283182</t>
+          <t xml:space="preserve">311283186</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-09</t>
+          <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7316,30 +7316,30 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringstedvej 43A</t>
+          <t xml:space="preserve">Skarridsøgade 37A</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">4440</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2390836</t>
+          <t xml:space="preserve">2388022</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J98">
-        <v>262</v>
+        <v>528</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283188</t>
+          <t xml:space="preserve">311283186</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7391,17 +7391,17 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skarridsøgade 37</t>
+          <t xml:space="preserve">Udbyvej 44</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2388022</t>
+          <t xml:space="preserve">2395636</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -7410,11 +7410,11 @@
         </is>
       </c>
       <c r="J99">
-        <v>2632</v>
+        <v>396</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283186</t>
+          <t xml:space="preserve">311287525</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-10</t>
+          <t xml:space="preserve">2027-12-06</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7466,30 +7466,30 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skarridsøgade 37A</t>
+          <t xml:space="preserve">Udbyvej 42</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2388022</t>
+          <t xml:space="preserve">2395380</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J100">
-        <v>528</v>
+        <v>872</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283186</t>
+          <t xml:space="preserve">311287726</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-10</t>
+          <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udbyvej 44</t>
+          <t xml:space="preserve">Udbyvej 42</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7551,20 +7551,20 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395636</t>
+          <t xml:space="preserve">2395380</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J101">
-        <v>396</v>
+        <v>672</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287525</t>
+          <t xml:space="preserve">311287726</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-06</t>
+          <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7631,11 +7631,11 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J102">
-        <v>872</v>
+        <v>330</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -7706,11 +7706,11 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J103">
-        <v>672</v>
+        <v>527</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udbyvej 42</t>
+          <t xml:space="preserve">Udby Kirkevej 21</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7776,20 +7776,20 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395380</t>
+          <t xml:space="preserve">2395597</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J104">
-        <v>330</v>
+        <v>1691</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287726</t>
+          <t xml:space="preserve">311288089</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-07</t>
+          <t xml:space="preserve">2027-12-11</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udbyvej 42</t>
+          <t xml:space="preserve">Udby Kirkevej 23</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7851,20 +7851,20 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395380</t>
+          <t xml:space="preserve">2395597</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J105">
-        <v>527</v>
+        <v>2066</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287726</t>
+          <t xml:space="preserve">311289980</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-07</t>
+          <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udby Kirkevej 21</t>
+          <t xml:space="preserve">Vandtårnsvej 6</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7926,20 +7926,20 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395597</t>
+          <t xml:space="preserve">5339301</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J106">
-        <v>1691</v>
+        <v>503</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288089</t>
+          <t xml:space="preserve">311295412</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-11</t>
+          <t xml:space="preserve">2028-01-31</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7991,17 +7991,17 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udby Kirkevej 23</t>
+          <t xml:space="preserve">Lersøparken 142</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395597</t>
+          <t xml:space="preserve">7416498</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -8010,11 +8010,11 @@
         </is>
       </c>
       <c r="J107">
-        <v>2066</v>
+        <v>606</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289980</t>
+          <t xml:space="preserve">311307671</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-21</t>
+          <t xml:space="preserve">2028-04-11</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8066,17 +8066,17 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandtårnsvej 6</t>
+          <t xml:space="preserve">Solvænget 1</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339301</t>
+          <t xml:space="preserve">2408810</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -8085,11 +8085,11 @@
         </is>
       </c>
       <c r="J108">
-        <v>503</v>
+        <v>275</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295412</t>
+          <t xml:space="preserve">311307633</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-31</t>
+          <t xml:space="preserve">2028-04-11</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8141,30 +8141,30 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lersøparken 142</t>
+          <t xml:space="preserve">Solvænget 11</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">7416498</t>
+          <t xml:space="preserve">2408810</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J109">
-        <v>606</v>
+        <v>275</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307671</t>
+          <t xml:space="preserve">311307633</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solvænget 1</t>
+          <t xml:space="preserve">Solvænget 6</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J110">
@@ -8291,30 +8291,30 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solvænget 11</t>
+          <t xml:space="preserve">Højgårdsvej 24</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4350</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408810</t>
+          <t xml:space="preserve">2410722, 100800374</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J111">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307633</t>
+          <t xml:space="preserve">311307933</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-11</t>
+          <t xml:space="preserve">2028-04-12</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8366,30 +8366,30 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solvænget 6</t>
+          <t xml:space="preserve">Sofiesminde Alle 5</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408810</t>
+          <t xml:space="preserve">100011737</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J112">
-        <v>275</v>
+        <v>991</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307633</t>
+          <t xml:space="preserve">311308315</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-11</t>
+          <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8441,17 +8441,17 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højgårdsvej 24</t>
+          <t xml:space="preserve">Tjørnegården 1</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">4350</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2410722, 100800374</t>
+          <t xml:space="preserve">10055688</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -8460,11 +8460,11 @@
         </is>
       </c>
       <c r="J113">
-        <v>262</v>
+        <v>1354</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307933</t>
+          <t xml:space="preserve">311308295</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-12</t>
+          <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofiesminde Alle 5</t>
+          <t xml:space="preserve">Havnevej 7</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8526,20 +8526,20 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">100011737</t>
+          <t xml:space="preserve">5334808</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J114">
-        <v>991</v>
+        <v>1048</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308315</t>
+          <t xml:space="preserve">311342403</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-13</t>
+          <t xml:space="preserve">2028-10-19</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnegården 1</t>
+          <t xml:space="preserve">Jernbanevej 29A</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">10055688</t>
+          <t xml:space="preserve">267924, 267925, 267926</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -8610,11 +8610,11 @@
         </is>
       </c>
       <c r="J115">
-        <v>1354</v>
+        <v>600</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308295</t>
+          <t xml:space="preserve">311352731</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-13</t>
+          <t xml:space="preserve">2028-12-20</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8666,30 +8666,30 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 7</t>
+          <t xml:space="preserve">Søbæksvej 30</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334808</t>
+          <t xml:space="preserve">270575</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J116">
-        <v>1048</v>
+        <v>2562</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311342403</t>
+          <t xml:space="preserve">311354541</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-19</t>
+          <t xml:space="preserve">2029-01-14</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanevej 29A</t>
+          <t xml:space="preserve">Omfartsvejen 27</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">267924, 267925, 267926</t>
+          <t xml:space="preserve">8282784</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -8760,21 +8760,21 @@
         </is>
       </c>
       <c r="J117">
-        <v>600</v>
+        <v>353</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352731</t>
+          <t xml:space="preserve">311403255</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-20</t>
+          <t xml:space="preserve">2029-10-10</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8816,17 +8816,17 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søbæksvej 30</t>
+          <t xml:space="preserve">Dampmøllevej 2</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">270575</t>
+          <t xml:space="preserve">7380402</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -8835,21 +8835,21 @@
         </is>
       </c>
       <c r="J118">
-        <v>2562</v>
+        <v>1944</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311354541</t>
+          <t xml:space="preserve">311448909</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-14</t>
+          <t xml:space="preserve">2030-07-09</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omfartsvejen 27</t>
+          <t xml:space="preserve">Ladegårdsparken Vest 167</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">8282784</t>
+          <t xml:space="preserve">5339287</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -8910,21 +8910,21 @@
         </is>
       </c>
       <c r="J119">
-        <v>353</v>
+        <v>840</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311403255</t>
+          <t xml:space="preserve">311658138</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-10</t>
+          <t xml:space="preserve">2033-02-06</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8966,17 +8966,17 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dampmøllevej 2</t>
+          <t xml:space="preserve">Skolevej 37</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4440</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">7380402</t>
+          <t xml:space="preserve">2389399</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -8985,21 +8985,21 @@
         </is>
       </c>
       <c r="J120">
-        <v>1944</v>
+        <v>1723</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311448909</t>
+          <t xml:space="preserve">311735788</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">ISOLINK ApS</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-09</t>
+          <t xml:space="preserve">2034-01-26</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ladegårdsparken Vest 167</t>
+          <t xml:space="preserve">Skolevej 4</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4532</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339287</t>
+          <t xml:space="preserve">2384021</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -9060,21 +9060,21 @@
         </is>
       </c>
       <c r="J121">
-        <v>840</v>
+        <v>1872</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311658138</t>
+          <t xml:space="preserve">311834296</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">CB Group ApS</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-06</t>
+          <t xml:space="preserve">2035-05-26</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9116,40 +9116,40 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 37</t>
+          <t xml:space="preserve">Skolevej 4</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">4440</t>
+          <t xml:space="preserve">4532</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2389399</t>
+          <t xml:space="preserve">2384021</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J122">
-        <v>1723</v>
+        <v>4238</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311735788</t>
+          <t xml:space="preserve">311834295</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISOLINK ApS</t>
+          <t xml:space="preserve">CB Group ApS</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-26</t>
+          <t xml:space="preserve">2035-05-26</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,17 +9191,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 4</t>
+          <t xml:space="preserve">Vandtårnsvej 3</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">4532</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2384021</t>
+          <t xml:space="preserve">10056287</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -9210,11 +9210,11 @@
         </is>
       </c>
       <c r="J123">
-        <v>1872</v>
+        <v>11883</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311834296</t>
+          <t xml:space="preserve">311834297</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9266,30 +9266,30 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 4</t>
+          <t xml:space="preserve">Bispehøjen 2</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">4532</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2384021</t>
+          <t xml:space="preserve">5338074</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J124">
-        <v>4238</v>
+        <v>1440</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311834295</t>
+          <t xml:space="preserve">311850583</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-26</t>
+          <t xml:space="preserve">2035-08-21</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandtårnsvej 3</t>
+          <t xml:space="preserve">Bispehøjen 2</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9351,20 +9351,20 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">10056287</t>
+          <t xml:space="preserve">5338074</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J125">
-        <v>11883</v>
+        <v>301</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311834297</t>
+          <t xml:space="preserve">311850584</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-26</t>
+          <t xml:space="preserve">2035-08-21</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J126">
@@ -9506,15 +9506,15 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J127">
-        <v>301</v>
+        <v>1963</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850586</t>
+          <t xml:space="preserve">311850583</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9581,11 +9581,11 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J128">
-        <v>1440</v>
+        <v>477</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -9656,11 +9656,11 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J129">
-        <v>1963</v>
+        <v>1685</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -9731,15 +9731,15 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J130">
-        <v>477</v>
+        <v>2108</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850583</t>
+          <t xml:space="preserve">311850584</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9806,11 +9806,11 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J131">
-        <v>1685</v>
+        <v>1440</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -9866,30 +9866,30 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bispehøjen 2</t>
+          <t xml:space="preserve">Holbækvej 108</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5338074</t>
+          <t xml:space="preserve">7226325</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J132">
-        <v>2108</v>
+        <v>1188</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850588</t>
+          <t xml:space="preserve">311851447</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-21</t>
+          <t xml:space="preserve">2035-08-26</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9941,30 +9941,30 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bispehøjen 2</t>
+          <t xml:space="preserve">Holbækvej 108</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5338074</t>
+          <t xml:space="preserve">7226325</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J133">
-        <v>1440</v>
+        <v>747</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850583</t>
+          <t xml:space="preserve">311851452</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-21</t>
+          <t xml:space="preserve">2035-08-26</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -10031,11 +10031,11 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="J134">
-        <v>1188</v>
+        <v>431</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -10106,15 +10106,15 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J135">
-        <v>747</v>
+        <v>2038</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851452</t>
+          <t xml:space="preserve">311851447</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10181,11 +10181,11 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J136">
-        <v>431</v>
+        <v>735</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -10256,11 +10256,11 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J137">
-        <v>2038</v>
+        <v>735</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -10331,11 +10331,11 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J138">
-        <v>735</v>
+        <v>1010</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -10406,11 +10406,11 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J139">
-        <v>735</v>
+        <v>385</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -10481,11 +10481,11 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J140">
-        <v>1010</v>
+        <v>379</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -10541,30 +10541,30 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 108</t>
+          <t xml:space="preserve">Hovedgaden 42</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4350</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">7226325</t>
+          <t xml:space="preserve">2410274</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J141">
-        <v>385</v>
+        <v>3739</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851447</t>
+          <t xml:space="preserve">311852051</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-26</t>
+          <t xml:space="preserve">2035-08-28</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10616,30 +10616,30 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 108</t>
+          <t xml:space="preserve">Hovedgaden 42</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4350</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">7226325</t>
+          <t xml:space="preserve">7564740</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J142">
-        <v>379</v>
+        <v>640</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851447</t>
+          <t xml:space="preserve">311852047</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-26</t>
+          <t xml:space="preserve">2035-08-28</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 42</t>
+          <t xml:space="preserve">Højgårdsvej 23</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -10701,20 +10701,20 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2410274</t>
+          <t xml:space="preserve">7564740</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J143">
-        <v>3739</v>
+        <v>261</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852051</t>
+          <t xml:space="preserve">311852046</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10766,30 +10766,30 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 42</t>
+          <t xml:space="preserve">Tølløsevej 64</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">4350</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">7564740</t>
+          <t xml:space="preserve">7376334</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J144">
-        <v>640</v>
+        <v>1242</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852047</t>
+          <t xml:space="preserve">311852541</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-28</t>
+          <t xml:space="preserve">2035-08-29</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,17 +10841,17 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højgårdsvej 23</t>
+          <t xml:space="preserve">Gl Ringstedvej 32</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">4350</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">7564740</t>
+          <t xml:space="preserve">5339867</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -10860,11 +10860,11 @@
         </is>
       </c>
       <c r="J145">
-        <v>261</v>
+        <v>487</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852046</t>
+          <t xml:space="preserve">311852735</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-28</t>
+          <t xml:space="preserve">2035-09-01</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,30 +10916,30 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tølløsevej 64</t>
+          <t xml:space="preserve">Gl Ringstedvej 32</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">7376334</t>
+          <t xml:space="preserve">5339867</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J146">
-        <v>1242</v>
+        <v>348</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852541</t>
+          <t xml:space="preserve">311852735</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-29</t>
+          <t xml:space="preserve">2035-09-01</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -11006,11 +11006,11 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J147">
-        <v>487</v>
+        <v>429</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -11081,11 +11081,11 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J148">
-        <v>348</v>
+        <v>396</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -11156,11 +11156,11 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J149">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J150">
@@ -11306,11 +11306,11 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J151">
-        <v>439</v>
+        <v>1293</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -11381,11 +11381,11 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J152">
-        <v>396</v>
+        <v>251</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Ringstedvej 32</t>
+          <t xml:space="preserve">Peder Billesvej 57</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11456,11 +11456,11 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J153">
-        <v>1293</v>
+        <v>579</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Ringstedvej 32</t>
+          <t xml:space="preserve">Anders Larsensvej 1</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11526,20 +11526,20 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339867</t>
+          <t xml:space="preserve">8285343</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J154">
-        <v>251</v>
+        <v>1404</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852735</t>
+          <t xml:space="preserve">311864985</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-01</t>
+          <t xml:space="preserve">2035-10-29</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peder Billesvej 57</t>
+          <t xml:space="preserve">Anders Larsensvej 3</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11601,20 +11601,20 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339867</t>
+          <t xml:space="preserve">8285343</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J155">
-        <v>579</v>
+        <v>324</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852735</t>
+          <t xml:space="preserve">311864983</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-01</t>
+          <t xml:space="preserve">2035-10-29</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anders Larsensvej 1</t>
+          <t xml:space="preserve">Anders Larsensvej 5</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11681,11 +11681,11 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J156">
-        <v>1404</v>
+        <v>2398</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anders Larsensvej 3</t>
+          <t xml:space="preserve">Damvej 19B</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">8285343</t>
+          <t xml:space="preserve">719717, 2384607</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -11760,11 +11760,11 @@
         </is>
       </c>
       <c r="J157">
-        <v>324</v>
+        <v>1096</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864983</t>
+          <t xml:space="preserve">311865044</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11816,17 +11816,17 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anders Larsensvej 5</t>
+          <t xml:space="preserve">Sportsvej 3</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">8285343</t>
+          <t xml:space="preserve">7376333</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -11835,11 +11835,11 @@
         </is>
       </c>
       <c r="J158">
-        <v>2398</v>
+        <v>2665</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864985</t>
+          <t xml:space="preserve">311864976</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11891,30 +11891,30 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damvej 19B</t>
+          <t xml:space="preserve">Sportsvej 3</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">719717, 2384607</t>
+          <t xml:space="preserve">7376333</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J159">
-        <v>1096</v>
+        <v>2066</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865044</t>
+          <t xml:space="preserve">311864976</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11981,11 +11981,11 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J160">
-        <v>2665</v>
+        <v>1115</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
@@ -12056,15 +12056,15 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J161">
-        <v>2066</v>
+        <v>466</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864976</t>
+          <t xml:space="preserve">311864978</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12116,30 +12116,30 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 3</t>
+          <t xml:space="preserve">Vandtårnsvej 10</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">7376333</t>
+          <t xml:space="preserve">5339264</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J162">
-        <v>1115</v>
+        <v>2285</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864976</t>
+          <t xml:space="preserve">311865119</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12191,30 +12191,30 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 3</t>
+          <t xml:space="preserve">Vandtårnsvej 14</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">7376333</t>
+          <t xml:space="preserve">8077972</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J163">
-        <v>466</v>
+        <v>280</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864978</t>
+          <t xml:space="preserve">311865122</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandtårnsvej 10</t>
+          <t xml:space="preserve">Mellemvang 7</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339264</t>
+          <t xml:space="preserve">5340835</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -12285,11 +12285,11 @@
         </is>
       </c>
       <c r="J164">
-        <v>2285</v>
+        <v>283</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865119</t>
+          <t xml:space="preserve">311865496</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-29</t>
+          <t xml:space="preserve">2035-10-30</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12341,30 +12341,30 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandtårnsvej 14</t>
+          <t xml:space="preserve">Brøndevej 15</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4305</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">8077972</t>
+          <t xml:space="preserve">719735, 2395810</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J165">
-        <v>280</v>
+        <v>1542</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865122</t>
+          <t xml:space="preserve">311865658</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-29</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemvang 7</t>
+          <t xml:space="preserve">Parallelvej 52</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,20 +12426,20 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340835</t>
+          <t xml:space="preserve">5335410</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J166">
-        <v>283</v>
+        <v>739</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865496</t>
+          <t xml:space="preserve">311866225</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-30</t>
+          <t xml:space="preserve">2035-11-04</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12491,30 +12491,30 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndevej 15</t>
+          <t xml:space="preserve">Parallelvej 52</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">4305</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">719735, 2395810</t>
+          <t xml:space="preserve">5335410</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J167">
-        <v>1542</v>
+        <v>640</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865658</t>
+          <t xml:space="preserve">311866227</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-31</t>
+          <t xml:space="preserve">2035-11-04</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12566,30 +12566,30 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 52</t>
+          <t xml:space="preserve">Skamstrupvej 18</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4440</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335410</t>
+          <t xml:space="preserve">2391265</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J168">
-        <v>739</v>
+        <v>1511</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866225</t>
+          <t xml:space="preserve">311866718</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-04</t>
+          <t xml:space="preserve">2035-11-06</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12641,30 +12641,30 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 52</t>
+          <t xml:space="preserve">Skamstrupvej 18</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4440</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335410</t>
+          <t xml:space="preserve">2391265</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J169">
-        <v>640</v>
+        <v>1990</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866227</t>
+          <t xml:space="preserve">311866718</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-04</t>
+          <t xml:space="preserve">2035-11-06</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12731,11 +12731,11 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J170">
-        <v>1511</v>
+        <v>796</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -12806,11 +12806,11 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J171">
-        <v>1990</v>
+        <v>836</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -12866,30 +12866,30 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skamstrupvej 18</t>
+          <t xml:space="preserve">Østergårdsvej 49</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">4440</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391265</t>
+          <t xml:space="preserve">2402461</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J172">
-        <v>796</v>
+        <v>1804</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866718</t>
+          <t xml:space="preserve">311867558</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-06</t>
+          <t xml:space="preserve">2035-11-11</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12941,30 +12941,30 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skamstrupvej 18</t>
+          <t xml:space="preserve">Østergårdsvej 51A</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">4440</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391265</t>
+          <t xml:space="preserve">2402461</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J173">
-        <v>836</v>
+        <v>280</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866718</t>
+          <t xml:space="preserve">311867559</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-06</t>
+          <t xml:space="preserve">2035-11-11</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergårdsvej 49</t>
+          <t xml:space="preserve">Østergårdsvej 53A</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402461</t>
+          <t xml:space="preserve">8820316</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -13035,11 +13035,11 @@
         </is>
       </c>
       <c r="J174">
-        <v>1804</v>
+        <v>729</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867558</t>
+          <t xml:space="preserve">311867560</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13091,30 +13091,30 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergårdsvej 51A</t>
+          <t xml:space="preserve">Bygaden 50</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4305</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402461</t>
+          <t xml:space="preserve">2395798</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J175">
-        <v>280</v>
+        <v>467</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867559</t>
+          <t xml:space="preserve">311867756</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-11</t>
+          <t xml:space="preserve">2035-11-12</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13166,17 +13166,17 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergårdsvej 53A</t>
+          <t xml:space="preserve">Orø Havn 3</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4305</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">8820316</t>
+          <t xml:space="preserve">2395790</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -13185,11 +13185,11 @@
         </is>
       </c>
       <c r="J176">
-        <v>729</v>
+        <v>452</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867560</t>
+          <t xml:space="preserve">311868836</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-11</t>
+          <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13241,30 +13241,30 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 50</t>
+          <t xml:space="preserve">Krogvejen 4</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">4305</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395798</t>
+          <t xml:space="preserve">2397479</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J177">
-        <v>467</v>
+        <v>427</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867756</t>
+          <t xml:space="preserve">311872573</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-12</t>
+          <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13316,30 +13316,30 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orø Havn 3</t>
+          <t xml:space="preserve">Krogvejen 4</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">4305</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395790</t>
+          <t xml:space="preserve">2397479</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J178">
-        <v>452</v>
+        <v>645</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868836</t>
+          <t xml:space="preserve">311872573</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-18</t>
+          <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13406,11 +13406,11 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J179">
-        <v>427</v>
+        <v>320</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
@@ -13481,11 +13481,11 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J180">
-        <v>645</v>
+        <v>1402</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -13556,15 +13556,15 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J181">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872573</t>
+          <t xml:space="preserve">311872576</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13616,30 +13616,30 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogvejen 4</t>
+          <t xml:space="preserve">Stestrupvej 41A</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4360</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2397479</t>
+          <t xml:space="preserve">2400079, 100800056</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J182">
-        <v>1402</v>
+        <v>1084</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872573</t>
+          <t xml:space="preserve">311874431</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-09</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13691,30 +13691,30 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogvejen 4</t>
+          <t xml:space="preserve">Stestrupvej 41B</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4360</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2397479</t>
+          <t xml:space="preserve">2400080, 100800076</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J183">
-        <v>290</v>
+        <v>1469</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872576</t>
+          <t xml:space="preserve">311874429</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-09</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13766,17 +13766,17 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stestrupvej 41A</t>
+          <t xml:space="preserve">Hesseløvej 12</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">4360</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2400079, 100800056</t>
+          <t xml:space="preserve">7153439</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -13785,11 +13785,11 @@
         </is>
       </c>
       <c r="J184">
-        <v>1084</v>
+        <v>960</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874431</t>
+          <t xml:space="preserve">311875725</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-19</t>
+          <t xml:space="preserve">2036-01-08</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13841,30 +13841,30 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stestrupvej 41B</t>
+          <t xml:space="preserve">Kalvemosevej 1</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">4360</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2400080, 100800076</t>
+          <t xml:space="preserve">100459791</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J185">
-        <v>1469</v>
+        <v>379</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874432</t>
+          <t xml:space="preserve">311880095</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-19</t>
+          <t xml:space="preserve">2036-02-03</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13916,40 +13916,40 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hesseløvej 12</t>
+          <t xml:space="preserve">Hovedgaden 36A</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4420</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">7153439</t>
+          <t xml:space="preserve">2402019</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J186">
-        <v>960</v>
+        <v>348</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875725</t>
+          <t xml:space="preserve">311882274</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve">CB Group ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-08</t>
+          <t xml:space="preserve">2036-02-16</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13991,30 +13991,30 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalvemosevej 1</t>
+          <t xml:space="preserve">Hovedgaden 36A</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4420</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">100459791</t>
+          <t xml:space="preserve">2402027</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J187">
-        <v>379</v>
+        <v>879</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880095</t>
+          <t xml:space="preserve">311882268</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-03</t>
+          <t xml:space="preserve">2036-02-16</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14076,12 +14076,12 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402019</t>
+          <t xml:space="preserve">2402027</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J188">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882274</t>
+          <t xml:space="preserve">311882275</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 36A</t>
+          <t xml:space="preserve">Hovedgaden 36B</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402027</t>
+          <t xml:space="preserve">2402030</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -14160,11 +14160,11 @@
         </is>
       </c>
       <c r="J189">
-        <v>879</v>
+        <v>445</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882268</t>
+          <t xml:space="preserve">311882265</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 36A</t>
+          <t xml:space="preserve">Hovedgaden 36B</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -14226,20 +14226,20 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402027</t>
+          <t xml:space="preserve">2402030</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J190">
-        <v>348</v>
+        <v>592</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882275</t>
+          <t xml:space="preserve">311882266</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14291,17 +14291,17 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 36B</t>
+          <t xml:space="preserve">Kalvemosevej 3</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">4420</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402030</t>
+          <t xml:space="preserve">5340919</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -14310,11 +14310,11 @@
         </is>
       </c>
       <c r="J191">
-        <v>445</v>
+        <v>345</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882265</t>
+          <t xml:space="preserve">311882720</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14324,7 +14324,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-16</t>
+          <t xml:space="preserve">2036-02-18</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14366,40 +14366,40 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 36B</t>
+          <t xml:space="preserve">Kalvemosevej 3</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">4420</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402030</t>
+          <t xml:space="preserve">5340919</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J192">
-        <v>592</v>
+        <v>640</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882266</t>
+          <t xml:space="preserve">311882720</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CB Group ApS</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-16</t>
+          <t xml:space="preserve">2036-02-18</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14441,17 +14441,17 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalvemosevej 3</t>
+          <t xml:space="preserve">Stestrupvej 49</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4360</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340919</t>
+          <t xml:space="preserve">8921449</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -14460,11 +14460,11 @@
         </is>
       </c>
       <c r="J193">
-        <v>345</v>
+        <v>3302</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882720</t>
+          <t xml:space="preserve">311888237</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-18</t>
+          <t xml:space="preserve">2036-03-18</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14516,30 +14516,30 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalvemosevej 3</t>
+          <t xml:space="preserve">Stestrupvej 49</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4360</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340919</t>
+          <t xml:space="preserve">8921449</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J194">
-        <v>640</v>
+        <v>455</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882720</t>
+          <t xml:space="preserve">311888240</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-18</t>
+          <t xml:space="preserve">2036-03-18</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stestrupvej 49</t>
+          <t xml:space="preserve">Holbækvej 36</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">4360</t>
+          <t xml:space="preserve">4370</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">8921449</t>
+          <t xml:space="preserve">9167622</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -14610,11 +14610,11 @@
         </is>
       </c>
       <c r="J195">
-        <v>3302</v>
+        <v>1082</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888237</t>
+          <t xml:space="preserve">311893637</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14624,7 +14624,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-18</t>
+          <t xml:space="preserve">2036-04-13</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14666,17 +14666,17 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stestrupvej 49</t>
+          <t xml:space="preserve">Bøgen 1</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">4360</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">8921449</t>
+          <t xml:space="preserve">719732, 5336412</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -14685,11 +14685,11 @@
         </is>
       </c>
       <c r="J196">
-        <v>455</v>
+        <v>632</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888240</t>
+          <t xml:space="preserve">311898603</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-18</t>
+          <t xml:space="preserve">2036-05-04</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 36</t>
+          <t xml:space="preserve">Holbækvej 30C</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">9167622</t>
+          <t xml:space="preserve">2408102</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -14760,11 +14760,11 @@
         </is>
       </c>
       <c r="J197">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893637</t>
+          <t xml:space="preserve">311904052</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-13</t>
+          <t xml:space="preserve">2036-05-27</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14816,30 +14816,30 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgen 1</t>
+          <t xml:space="preserve">Holbækvej 34</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4370</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">719732, 5336412</t>
+          <t xml:space="preserve">719778, 2408102</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J198">
-        <v>632</v>
+        <v>2048</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898603</t>
+          <t xml:space="preserve">311904037</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14849,7 +14849,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-04</t>
+          <t xml:space="preserve">2036-05-27</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14891,17 +14891,17 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 30C</t>
+          <t xml:space="preserve">Hovedgaden 74</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">4370</t>
+          <t xml:space="preserve">4520</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408102</t>
+          <t xml:space="preserve">2391620</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -14910,11 +14910,11 @@
         </is>
       </c>
       <c r="J199">
-        <v>1080</v>
+        <v>722</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311904052</t>
+          <t xml:space="preserve">311903997</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -14966,30 +14966,30 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 34</t>
+          <t xml:space="preserve">Hovedgaden 74</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">4370</t>
+          <t xml:space="preserve">4520</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">719778, 2408102</t>
+          <t xml:space="preserve">2391620</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J200">
-        <v>2048</v>
+        <v>640</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311904037</t>
+          <t xml:space="preserve">311903995</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 74</t>
+          <t xml:space="preserve">Hovedgaden 76F</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -15056,15 +15056,15 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J201">
-        <v>722</v>
+        <v>441</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903997</t>
+          <t xml:space="preserve">311903995</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 74</t>
+          <t xml:space="preserve">Hovedgaden 76F</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -15131,11 +15131,11 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J202">
-        <v>640</v>
+        <v>654</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
@@ -15206,11 +15206,11 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J203">
-        <v>441</v>
+        <v>4699</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
@@ -15281,11 +15281,11 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J204">
-        <v>654</v>
+        <v>622</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
@@ -15341,30 +15341,30 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 76F</t>
+          <t xml:space="preserve">Hybenvang 61A</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">4520</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391620</t>
+          <t xml:space="preserve">265333, 265334</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J205">
-        <v>4699</v>
+        <v>418</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903995</t>
+          <t xml:space="preserve">311904008</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -15416,30 +15416,30 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 76F</t>
+          <t xml:space="preserve">Hybenvang 63</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">4520</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391620</t>
+          <t xml:space="preserve">5340689</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J206">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903995</t>
+          <t xml:space="preserve">311904029</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -15491,7 +15491,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hybenvang 61A</t>
+          <t xml:space="preserve">Nygade 9</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -15501,7 +15501,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">265333, 265334</t>
+          <t xml:space="preserve">7618119</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -15510,11 +15510,11 @@
         </is>
       </c>
       <c r="J207">
-        <v>418</v>
+        <v>4058</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311904008</t>
+          <t xml:space="preserve">311905846</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-27</t>
+          <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15566,7 +15566,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hybenvang 63</t>
+          <t xml:space="preserve">Nygade 9</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -15576,20 +15576,20 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340689</t>
+          <t xml:space="preserve">7618119</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J208">
-        <v>634</v>
+        <v>382</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311904029</t>
+          <t xml:space="preserve">311905846</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-27</t>
+          <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15641,17 +15641,17 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 9</t>
+          <t xml:space="preserve">Holbækvej 30B</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4370</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">7618119</t>
+          <t xml:space="preserve">2408076</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -15660,11 +15660,11 @@
         </is>
       </c>
       <c r="J209">
-        <v>4058</v>
+        <v>2062</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905846</t>
+          <t xml:space="preserve">311909485</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -15674,7 +15674,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-04</t>
+          <t xml:space="preserve">2036-06-19</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15716,17 +15716,17 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 9</t>
+          <t xml:space="preserve">Holbækvej 30F</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4370</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">7618119</t>
+          <t xml:space="preserve">2408076</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -15735,11 +15735,11 @@
         </is>
       </c>
       <c r="J210">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905846</t>
+          <t xml:space="preserve">311909486</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-04</t>
+          <t xml:space="preserve">2036-06-19</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15791,17 +15791,17 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 30B</t>
+          <t xml:space="preserve">Udby Kirkevej 25</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">4370</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408076</t>
+          <t xml:space="preserve">7960027</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -15810,11 +15810,11 @@
         </is>
       </c>
       <c r="J211">
-        <v>2062</v>
+        <v>519</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311909485</t>
+          <t xml:space="preserve">311910894</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15824,7 +15824,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-19</t>
+          <t xml:space="preserve">2036-06-25</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15866,17 +15866,17 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 30F</t>
+          <t xml:space="preserve">Kasernevej 43</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">4370</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408076</t>
+          <t xml:space="preserve">7095821</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -15885,11 +15885,11 @@
         </is>
       </c>
       <c r="J212">
-        <v>376</v>
+        <v>802</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311909486</t>
+          <t xml:space="preserve">311911466</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15899,7 +15899,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-19</t>
+          <t xml:space="preserve">2036-06-29</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udby Kirkevej 25</t>
+          <t xml:space="preserve">Kasernevej 43</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -15951,20 +15951,20 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">7960027</t>
+          <t xml:space="preserve">7095821</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J213">
-        <v>519</v>
+        <v>1348</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311910894</t>
+          <t xml:space="preserve">311911466</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-25</t>
+          <t xml:space="preserve">2036-06-29</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -16016,30 +16016,30 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kasernevej 43</t>
+          <t xml:space="preserve">Sportsvej 5</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">7095821</t>
+          <t xml:space="preserve">7376333</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J214">
-        <v>802</v>
+        <v>352</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911466</t>
+          <t xml:space="preserve">311911482</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kasernevej 43</t>
+          <t xml:space="preserve">Torpet 1</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -16101,20 +16101,20 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">7095821</t>
+          <t xml:space="preserve">10218277</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J215">
-        <v>1348</v>
+        <v>1088</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911466</t>
+          <t xml:space="preserve">311911479</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16166,40 +16166,40 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 5</t>
+          <t xml:space="preserve">Rensdyrvej 2</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">7376333</t>
+          <t xml:space="preserve">2399272</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J216">
-        <v>352</v>
+        <v>5665</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911482</t>
+          <t xml:space="preserve">311911823</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t xml:space="preserve">CB Group ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-29</t>
+          <t xml:space="preserve">2036-06-30</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -16241,40 +16241,40 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torpet 1</t>
+          <t xml:space="preserve">Rensdyrvej 4</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">10218277</t>
+          <t xml:space="preserve">2399272</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J217">
-        <v>1088</v>
+        <v>1315</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911479</t>
+          <t xml:space="preserve">311911823</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t xml:space="preserve">CB Group ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-29</t>
+          <t xml:space="preserve">2036-06-30</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rensdyrvej 2</t>
+          <t xml:space="preserve">Rensdyrvej 4</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -16331,11 +16331,11 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J218">
-        <v>5665</v>
+        <v>1277</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
@@ -16391,40 +16391,40 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rensdyrvej 4</t>
+          <t xml:space="preserve">Tuse Byvej 16</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399272</t>
+          <t xml:space="preserve">2393534</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J219">
-        <v>1315</v>
+        <v>2664</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911823</t>
+          <t xml:space="preserve">311912618</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CB Group ApS</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-30</t>
+          <t xml:space="preserve">2036-07-03</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -16466,17 +16466,17 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rensdyrvej 4</t>
+          <t xml:space="preserve">Tuse Byvej 16</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399272</t>
+          <t xml:space="preserve">2393534</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -16485,21 +16485,21 @@
         </is>
       </c>
       <c r="J220">
-        <v>1277</v>
+        <v>673</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911823</t>
+          <t xml:space="preserve">311912618</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CB Group ApS</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-30</t>
+          <t xml:space="preserve">2036-07-03</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -16541,30 +16541,30 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 16</t>
+          <t xml:space="preserve">Tølløsevej 58</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393534</t>
+          <t xml:space="preserve">2409847</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J221">
-        <v>2664</v>
+        <v>401</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311912618</t>
+          <t xml:space="preserve">311916428</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-03</t>
+          <t xml:space="preserve">2036-07-29</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16616,30 +16616,30 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 16</t>
+          <t xml:space="preserve">Tølløsevej 58</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393534</t>
+          <t xml:space="preserve">2409847</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J222">
-        <v>673</v>
+        <v>357</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311912618</t>
+          <t xml:space="preserve">311916427</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -16649,7 +16649,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-03</t>
+          <t xml:space="preserve">2036-07-29</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16706,15 +16706,15 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J223">
-        <v>401</v>
+        <v>506</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916428</t>
+          <t xml:space="preserve">311916426</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -16781,15 +16781,15 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J224">
-        <v>357</v>
+        <v>978</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916427</t>
+          <t xml:space="preserve">311916424</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -16841,30 +16841,30 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tølløsevej 58</t>
+          <t xml:space="preserve">Asmindrupvej 50</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2409847</t>
+          <t xml:space="preserve">2399271</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J225">
-        <v>506</v>
+        <v>589</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916426</t>
+          <t xml:space="preserve">311917298</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-29</t>
+          <t xml:space="preserve">2036-08-04</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16916,17 +16916,17 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tølløsevej 58</t>
+          <t xml:space="preserve">Ellebjergvej 31A</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2409847</t>
+          <t xml:space="preserve">2387969</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -16935,11 +16935,11 @@
         </is>
       </c>
       <c r="J226">
-        <v>978</v>
+        <v>297</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916424</t>
+          <t xml:space="preserve">311919655</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -16949,7 +16949,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-29</t>
+          <t xml:space="preserve">2036-08-17</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16991,17 +16991,17 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asmindrupvej 50</t>
+          <t xml:space="preserve">Skovlystvej 2</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399271</t>
+          <t xml:space="preserve">2386579</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -17010,11 +17010,11 @@
         </is>
       </c>
       <c r="J227">
-        <v>589</v>
+        <v>1668</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311917298</t>
+          <t xml:space="preserve">311919644</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-04</t>
+          <t xml:space="preserve">2036-08-17</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -17066,30 +17066,30 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ellebjergvej 31A</t>
+          <t xml:space="preserve">Tuse Byvej 2</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2387969</t>
+          <t xml:space="preserve">2393546</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J228">
-        <v>297</v>
+        <v>7356</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311919655</t>
+          <t xml:space="preserve">311919716</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -17141,30 +17141,30 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovlystvej 2</t>
+          <t xml:space="preserve">Tuse Byvej 2</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2386579</t>
+          <t xml:space="preserve">2393546</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J229">
-        <v>1668</v>
+        <v>355</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311919644</t>
+          <t xml:space="preserve">311919716</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 2</t>
+          <t xml:space="preserve">Tuse Byvej 8</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -17226,20 +17226,20 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393546</t>
+          <t xml:space="preserve">2393535</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J230">
-        <v>7356</v>
+        <v>308</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311919716</t>
+          <t xml:space="preserve">311919722</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -17291,30 +17291,30 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 2</t>
+          <t xml:space="preserve">Elmegården 56</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393546</t>
+          <t xml:space="preserve">2388160</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J231">
-        <v>355</v>
+        <v>1393</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311919716</t>
+          <t xml:space="preserve">311920764</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-17</t>
+          <t xml:space="preserve">2036-08-21</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -17381,15 +17381,15 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J232">
-        <v>308</v>
+        <v>2701</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311919722</t>
+          <t xml:space="preserve">311921343</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -17399,7 +17399,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-17</t>
+          <t xml:space="preserve">2036-08-25</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -17441,30 +17441,30 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmegården 56</t>
+          <t xml:space="preserve">Mellemvang 9</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2388160</t>
+          <t xml:space="preserve">5340827</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J233">
-        <v>1393</v>
+        <v>1983</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311920764</t>
+          <t xml:space="preserve">311927578</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -17474,7 +17474,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-21</t>
+          <t xml:space="preserve">2036-09-23</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -17516,30 +17516,30 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 8</t>
+          <t xml:space="preserve">Centervænget 2</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393535</t>
+          <t xml:space="preserve">2399431</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J234">
-        <v>2701</v>
+        <v>326</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311921343</t>
+          <t xml:space="preserve">311928900</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -17549,7 +17549,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-25</t>
+          <t xml:space="preserve">2036-09-29</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -17591,30 +17591,30 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemvang 9</t>
+          <t xml:space="preserve">Centervænget 4</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340827</t>
+          <t xml:space="preserve">2399431</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J235">
-        <v>1983</v>
+        <v>400</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311927578</t>
+          <t xml:space="preserve">311928900</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -17624,7 +17624,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-23</t>
+          <t xml:space="preserve">2036-09-29</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17666,30 +17666,30 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Centervænget 2</t>
+          <t xml:space="preserve">Kasernevej 6</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399431</t>
+          <t xml:space="preserve">8033723</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J236">
-        <v>326</v>
+        <v>2314</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928900</t>
+          <t xml:space="preserve">311930138</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-29</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17741,30 +17741,30 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Centervænget 4</t>
+          <t xml:space="preserve">Brændholtvej 5</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4350</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399431</t>
+          <t xml:space="preserve">2410400</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J237">
-        <v>400</v>
+        <v>713</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928900</t>
+          <t xml:space="preserve">311931053</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -17774,7 +17774,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-29</t>
+          <t xml:space="preserve">2036-10-09</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
